--- a/AscendOS-Hardware-Requirements.xlsx
+++ b/AscendOS-Hardware-Requirements.xlsx
@@ -185,7 +185,7 @@
     <row r="6" ht="55.8" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AscendOS is a browser-delivered platform. Code Compass answers building-code questions against an ingested vector corpus; Code Inspector analyses site photographs. Both are short, bursty jobs that hold a CPU core briefly and release it, and both spend most of their time waiting on a model API rather than computing. The fleet is therefore sized on how many jobs run AT THE SAME INSTANT, not on seat count.</t>
+          <t xml:space="preserve">AscendOS is a browser-delivered platform. Code Compass answers building-code questions against an ingested vector corpus; Code Inspector analyses site photographs. Both are short, bursty jobs that hold a CPU core for seconds and then release it, and both spend most of their time waiting on a model API rather than computing. The fleet is therefore sized on how many jobs run AT THE SAME INSTANT, not on seat count.</t>
         </is>
       </c>
     </row>
@@ -200,7 +200,7 @@
     <row r="9" ht="69" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Jobs at once" - the number of searches and photo scans in flight at the SAME INSTANT, at the busiest moment of the busiest day. Not jobs per day, and not people signed in. A search holds a CPU core for a second or two and then releases it, which is why a few thousand searches a day resolve to a handful running simultaneously. This is the figure that determines hardware. It appears as two columns because usage is a range, and every machine figure is sized on the busier of the two.</t>
+          <t xml:space="preserve">"Jobs at once" - the number of searches and photo scans in flight at the SAME INSTANT, at the busiest moment of the busiest day. Not jobs per day, and not people signed in. A Compass search holds a CPU core for about 12 seconds and an Inspector scan about 55, then releases it, which is why a few thousand searches a day resolve to a handful running at any one moment. This is the figure that determines hardware. It appears as two columns because usage is a range, and every machine figure is sized on the busier of the two.</t>
         </is>
       </c>
     </row>
@@ -211,177 +211,249 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="29.4" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="6" customHeight="1"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What a number like 0.5 means — and why it is not half a machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29.4" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A value below 1 is normal. 0.5 means that during the busiest hour a job is in progress about half the time, and nothing is running the rest of it. Worked through at 20 seats:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.2" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   20 seats x 20 searches a day                          =  400 searches a day</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16.2" customHeight="1">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   spread across an 8-hour working day                   =   50 an hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.2" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the busy hour runs at 3x the daily average            =  150 an hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.2" customHeight="1">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   each search occupies a core for about 12 seconds      =  150 x 12s = 1,800 core-seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.2" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1,800 seconds of work inside a 3,600-second hour      =  0.5 JOBS AT ONCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42.6" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You cannot buy half a server, and nothing here suggests you should. Every option starts at one machine; this figure describes how hard that machine is worked. It only begins to drive the hardware once it climbs past 1, and it climbs in proportion to seats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42.6" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is an average, not a ceiling. Arrivals are random, so a figure of 0.5 still produces brief moments with two or three jobs at once. Absorbing those is exactly what the gap between the computed requirement and the provisioned machines is for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="29.4" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job lengths differ by module: a Compass search runs about 12 seconds, an Inspector photo scan about 55 seconds. That is why a few hundred Inspector users move this number more than several hundred extra Compass seats do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="29.4" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">These are CAPACITY figures, not availability figures. A single instance of anything is a single point of failure; designing for redundancy would at minimum double the application tier and is a separate decision.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The three options — alternatives, not layers</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42.6" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="26" ht="42.6" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">A · App Service (PaaS) — Premium v3 instances. Premium rather than Standard is deliberate: HTTP-driven autoscaling is Premium-only, Standard cannot be made zone-redundant, and Standard caps at 10 instances, a ceiling this range reaches. P0v3 (1 vCPU / 4 GB) is the scaling unit; P1v3 or P2v3 substitute at half or a quarter of the count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42.6" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B · Virtual Machines — Bsv2 burstable, the right family for spiky low-average load. B2s_v2 and larger bank credits at a 40% base and utilisation here sits well below that. Sized for fewest machines, since operating them is the real cost of this option.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="29.4" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C · Container Apps — request-scaled replicas at a fixed 1 vCPU : 2 GiB ratio, max 4 vCPU / 8 GiB each, scaling to zero. Unavoidably a hybrid: the search index cannot live here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Does Azure change the requirement? No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="55.8" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peak concurrency, required cores, required memory and index size are properties of the workload and would be identical on any provider. What Azure changes is the ladder of purchasable units, plus two constraints on the shape of the deployment: the search index can never share a machine on options A or C, and Standard App Service’s instance cap forces Premium for this range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The search index is the one forced decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="69" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The index is Qdrant, which requires block-level storage with a POSIX filesystem and explicitly does not run on network filesystems. App Service persistent storage is an SMB share and cannot take the exclusive locks a database needs; Container Apps offers only ephemeral storage and Azure Files. Neither can host it. A VM or AKS can, and Azure AI Search is the managed alternative — though that is an API rewrite, not a drop-in. There is no first-party managed Qdrant on Azure; the Marketplace listing is third-party SaaS. See the Search index tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Usage assumed</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="29.4" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code Compass: 15-20 searches per seat per working day. Code Inspector: 5-7 scans per user per working day, for the subset named in each block.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="29.4" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peak hour is sized at 3x the flat daily average, because real usage clusters at the start of the day and after lunch rather than spreading evenly.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42.6" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usage is a range, so every row is computed twice. All hardware figures follow the HIGH bound (20 searches, 7 scans) — a fleet sized on average usage is under-provisioned on every busy day. The low bound appears beside it in the concurrency columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reading the tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="29.4" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Required" is what the model computes. The machine columns show the smallest sensible allocation covering it, which is almost always more — that gap is deliberate headroom, not waste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="29.4" customHeight="1">
+          <t xml:space="preserve">B · Virtual Machines — Bsv2 burstable, the right family for spiky low-average load. B2s_v2 and larger bank credits at a 40% base and utilisation here sits well below that. Sized for fewest machines, since operating them is the real cost of this option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="29.4" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C · Container Apps — request-scaled replicas at a fixed 1 vCPU : 2 GiB ratio, max 4 vCPU / 8 GiB each, scaling to zero. Unavoidably a hybrid: the search index cannot live here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Does Azure change the requirement? No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="55.8" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">App RAM and index RAM are never summed. Application memory scales with concurrent jobs; the index is a fixed working set that grows with the corpus. On options A and C they are always on different machines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="55.8" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On Option B the index shares the web VM at small scale and separates later — Compass only at 480 seats, with 250 Inspector users at 200 seats (high usage). Those rows are shaded, and totals can fall there: one shared box had to satisfy the larger demand in every dimension at once, so two right-sized machines can total less than one oversized one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To confirm against your own subscription</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42.6" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regional vCPU quota is not published by Microsoft and varies by subscription type, age and region; a new subscription may have very low or zero quota in a given region. Quota and capacity are checked separately, so sufficient quota does not guarantee the sizes are available there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="29.4" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Azure AI Search higher quotas are unavailable in Israel Central, Qatar Central, Spain Central and South India, which remain on older limits.</t>
+          <t xml:space="preserve">Peak concurrency, required cores, required memory and index size are properties of the workload and would be identical on any provider. What Azure changes is the ladder of purchasable units, plus two constraints on the shape of the deployment: the search index can never share a machine on options A or C, and Standard App Service’s instance cap forces Premium for this range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The search index is the one forced decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="69" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The index is Qdrant, which requires block-level storage with a POSIX filesystem and explicitly does not run on network filesystems. App Service persistent storage is an SMB share and cannot take the exclusive locks a database needs; Container Apps offers only ephemeral storage and Azure Files. Neither can host it. A VM or AKS can, and Azure AI Search is the managed alternative — though that is an API rewrite, not a drop-in. There is no first-party managed Qdrant on Azure; the Marketplace listing is third-party SaaS. See the Search index tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usage assumed</t>
         </is>
       </c>
     </row>
     <row r="37" ht="29.4" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Code Compass: 15-20 searches per seat per working day. Code Inspector: 5-7 scans per user per working day, for the subset named in each block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="29.4" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peak hour is sized at 3x the flat daily average, because real usage clusters at the start of the day and after lunch rather than spreading evenly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42.6" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usage is a range, so every row is computed twice. All hardware figures follow the HIGH bound (20 searches, 7 scans) — a fleet sized on average usage is under-provisioned on every busy day. The low bound appears beside it in the concurrency columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="6" customHeight="1"/>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading the tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="29.4" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Required" is what the model computes. The machine columns show the smallest sensible allocation covering it, which is almost always more — that gap is deliberate headroom, not waste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="29.4" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App RAM and index RAM are never summed. Application memory scales with concurrent jobs; the index is a fixed working set that grows with the corpus. On options A and C they are always on different machines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="55.8" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Option B the index shares the web VM at small scale and separates later — Compass only at 480 seats, with 250 Inspector users at 200 seats (high usage). Those rows are shaded, and totals can fall there: one shared box had to satisfy the larger demand in every dimension at once, so two right-sized machines can total less than one oversized one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="6" customHeight="1"/>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To confirm against your own subscription</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42.6" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional vCPU quota is not published by Microsoft and varies by subscription type, age and region; a new subscription may have very low or zero quota in a given region. Quota and capacity are checked separately, so sufficient quota does not guarantee the sizes are available there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="29.4" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azure AI Search higher quotas are unavailable in Israel Central, Qatar Central, Spain Central and South India, which remain on older limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="29.4" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Premium v4 is GA with identical vCPU and RAM to v3 — faster processors and NVMe local storage only, so no extra capacity should be budgeted for it. It has no stable outbound IP addresses.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Not included</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="29.4" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="52" ht="29.4" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pricing. Also excluded: high availability and redundancy, which would at minimum double the web tier; developer and staging environments; CI; off-site backup targets. This is the production serving fleet only.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="16.2" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="16.2" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Scope: 20 to 840 seats in steps of 20, 42 rows per scenario.</t>
         </is>
@@ -437,129 +509,103 @@
     <row r="5" ht="42.6" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Jobs at once" - searches and photo scans in flight at the SAME INSTANT, at the busiest moment of the busiest day. Not jobs per day, and not people signed in. A job holds a CPU core for only a second or two, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="29.4" customHeight="1">
+          <t xml:space="preserve">"Jobs at once" - searches and photo scans running at the SAME MOMENT, averaged across the busiest hour. Not jobs per day, and not people signed in. A Compass search holds a CPU core for about 12 seconds and an Inspector scan about 55, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55.8" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">A value below 1 is normal and is NOT a fraction of a machine. 0.5 means a job is in progress about half the busy hour and nothing is running the rest of it. Every option starts at one machine regardless; this figure says how hard that machine is worked. It is an average, so brief moments with two or three jobs at once still occur - that is what the headroom is for. Full worked example on the Read Me tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29.4" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">"Machines to buy" - App Service plan instances plus the one VM holding the search index. "P0v3 x7" means seven instances of 1 vCPU / 4 GB each; with the index VM that is 8 machines.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass only</t>
         </is>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" ht="16.2" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" ht="16.2" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Every seat runs 15–20 Code Compass searches per working day.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0v3 x1</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F11" s="12">
-        <v>2</v>
-      </c>
-      <c r="G11" s="12">
-        <v>3</v>
-      </c>
-      <c r="H11" s="12">
-        <v>8</v>
-      </c>
-      <c r="I11" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
@@ -586,13 +632,13 @@
     </row>
     <row r="13">
       <c r="A13" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
@@ -619,13 +665,13 @@
     </row>
     <row r="14">
       <c r="A14" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B14" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="C14" s="4">
         <v>1.5</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
@@ -652,17 +698,17 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B15" s="4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="4">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x2</t>
+          <t xml:space="preserve">P0v3 x1</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -671,27 +717,27 @@
         </is>
       </c>
       <c r="F15" s="12">
+        <v>2</v>
+      </c>
+      <c r="G15" s="12">
         <v>3</v>
       </c>
-      <c r="G15" s="12">
-        <v>4</v>
-      </c>
       <c r="H15" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="C16" s="4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -718,13 +764,13 @@
     </row>
     <row r="17">
       <c r="A17" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B17" s="4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="C17" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -751,13 +797,13 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B18" s="4">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C18" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
@@ -784,13 +830,13 @@
     </row>
     <row r="19">
       <c r="A19" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B19" s="4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
@@ -817,13 +863,13 @@
     </row>
     <row r="20">
       <c r="A20" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B20" s="4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="C20" s="4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -850,13 +896,13 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B21" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C21" s="4">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
@@ -883,17 +929,17 @@
     </row>
     <row r="22">
       <c r="A22" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B22" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="C22" s="4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x3</t>
+          <t xml:space="preserve">P0v3 x2</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -902,13 +948,13 @@
         </is>
       </c>
       <c r="F22" s="12">
+        <v>3</v>
+      </c>
+      <c r="G22" s="12">
         <v>4</v>
       </c>
-      <c r="G22" s="12">
-        <v>5</v>
-      </c>
       <c r="H22" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12">
         <v>2</v>
@@ -916,13 +962,13 @@
     </row>
     <row r="23">
       <c r="A23" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B23" s="4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C23" s="4">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
@@ -944,18 +990,18 @@
         <v>16</v>
       </c>
       <c r="I23" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B24" s="4">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="C24" s="4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
@@ -982,13 +1028,13 @@
     </row>
     <row r="25">
       <c r="A25" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B25" s="4">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="C25" s="4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
@@ -1015,13 +1061,13 @@
     </row>
     <row r="26">
       <c r="A26" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B26" s="4">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="C26" s="4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
@@ -1048,13 +1094,13 @@
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B27" s="4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
@@ -1081,17 +1127,17 @@
     </row>
     <row r="28">
       <c r="A28" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B28" s="4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="C28" s="4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x4</t>
+          <t xml:space="preserve">P0v3 x3</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1100,13 +1146,13 @@
         </is>
       </c>
       <c r="F28" s="12">
+        <v>4</v>
+      </c>
+      <c r="G28" s="12">
         <v>5</v>
       </c>
-      <c r="G28" s="12">
-        <v>6</v>
-      </c>
       <c r="H28" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I28" s="12">
         <v>3</v>
@@ -1114,13 +1160,13 @@
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B29" s="4">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="C29" s="4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
@@ -1147,13 +1193,13 @@
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="C30" s="4">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
@@ -1180,13 +1226,13 @@
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B31" s="4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="C31" s="4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
@@ -1213,13 +1259,13 @@
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B32" s="4">
-        <v>8.3</v>
+        <v>7.9</v>
       </c>
       <c r="C32" s="4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
@@ -1241,18 +1287,18 @@
         <v>20</v>
       </c>
       <c r="I32" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B33" s="4">
-        <v>8.6</v>
+        <v>8.3</v>
       </c>
       <c r="C33" s="4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
@@ -1279,13 +1325,13 @@
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B34" s="4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="C34" s="4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
@@ -1312,17 +1358,17 @@
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B35" s="4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="C35" s="4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x5</t>
+          <t xml:space="preserve">P0v3 x4</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -1331,13 +1377,13 @@
         </is>
       </c>
       <c r="F35" s="12">
+        <v>5</v>
+      </c>
+      <c r="G35" s="12">
         <v>6</v>
       </c>
-      <c r="G35" s="12">
-        <v>7</v>
-      </c>
       <c r="H35" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I35" s="12">
         <v>4</v>
@@ -1345,13 +1391,13 @@
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B36" s="4">
-        <v>9.8</v>
+        <v>9.4</v>
       </c>
       <c r="C36" s="4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
@@ -1378,13 +1424,13 @@
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B37" s="4">
-        <v>10.1</v>
+        <v>9.8</v>
       </c>
       <c r="C37" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
@@ -1411,13 +1457,13 @@
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B38" s="4">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="C38" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
@@ -1444,13 +1490,13 @@
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B39" s="4">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="C39" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
@@ -1477,13 +1523,13 @@
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B40" s="4">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="C40" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
@@ -1505,18 +1551,18 @@
         <v>24</v>
       </c>
       <c r="I40" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B41" s="4">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="C41" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
@@ -1543,17 +1589,17 @@
     </row>
     <row r="42">
       <c r="A42" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B42" s="4">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="C42" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x6</t>
+          <t xml:space="preserve">P0v3 x5</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -1562,13 +1608,13 @@
         </is>
       </c>
       <c r="F42" s="12">
+        <v>6</v>
+      </c>
+      <c r="G42" s="12">
         <v>7</v>
       </c>
-      <c r="G42" s="12">
-        <v>8</v>
-      </c>
       <c r="H42" s="12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I42" s="12">
         <v>5</v>
@@ -1576,13 +1622,13 @@
     </row>
     <row r="43">
       <c r="A43" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B43" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C43" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
@@ -1609,13 +1655,13 @@
     </row>
     <row r="44">
       <c r="A44" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B44" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C44" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
@@ -1642,13 +1688,13 @@
     </row>
     <row r="45">
       <c r="A45" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B45" s="4">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="C45" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -1675,13 +1721,13 @@
     </row>
     <row r="46">
       <c r="A46" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B46" s="4">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="C46" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
@@ -1708,13 +1754,13 @@
     </row>
     <row r="47">
       <c r="A47" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B47" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C47" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
@@ -1741,17 +1787,17 @@
     </row>
     <row r="48">
       <c r="A48" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B48" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C48" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x7</t>
+          <t xml:space="preserve">P0v3 x6</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -1760,13 +1806,13 @@
         </is>
       </c>
       <c r="F48" s="12">
+        <v>7</v>
+      </c>
+      <c r="G48" s="12">
         <v>8</v>
       </c>
-      <c r="G48" s="12">
-        <v>9</v>
-      </c>
       <c r="H48" s="12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I48" s="12">
         <v>5</v>
@@ -1774,13 +1820,13 @@
     </row>
     <row r="49">
       <c r="A49" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B49" s="4">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="C49" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
@@ -1802,18 +1848,18 @@
         <v>32</v>
       </c>
       <c r="I49" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B50" s="4">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="C50" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
@@ -1822,7 +1868,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F50" s="12">
@@ -1832,7 +1878,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I50" s="12">
         <v>6</v>
@@ -1840,13 +1886,13 @@
     </row>
     <row r="51">
       <c r="A51" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B51" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C51" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
@@ -1873,13 +1919,13 @@
     </row>
     <row r="52">
       <c r="A52" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B52" s="4">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="C52" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
@@ -1904,122 +1950,122 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" ht="10" customHeight="1"/>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9">
+        <v>840</v>
+      </c>
+      <c r="B53" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="C53" s="4">
+        <v>21</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0v3 x7</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F53" s="12">
+        <v>8</v>
+      </c>
+      <c r="G53" s="12">
+        <v>9</v>
+      </c>
+      <c r="H53" s="12">
+        <v>36</v>
+      </c>
+      <c r="I53" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" ht="10" customHeight="1"/>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 200 Code Inspector users</t>
         </is>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" ht="16.2" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" ht="16.2" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 200 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9">
-        <v>20</v>
-      </c>
-      <c r="B57" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C57" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0v3 x1</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F57" s="12">
-        <v>2</v>
-      </c>
-      <c r="G57" s="12">
-        <v>3</v>
-      </c>
-      <c r="H57" s="12">
-        <v>8</v>
-      </c>
-      <c r="I57" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B58" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C58" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x2</t>
+          <t xml:space="preserve">P0v3 x1</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -2028,13 +2074,13 @@
         </is>
       </c>
       <c r="F58" s="12">
+        <v>2</v>
+      </c>
+      <c r="G58" s="12">
         <v>3</v>
       </c>
-      <c r="G58" s="12">
-        <v>4</v>
-      </c>
       <c r="H58" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I58" s="12">
         <v>1</v>
@@ -2042,13 +2088,13 @@
     </row>
     <row r="59">
       <c r="A59" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B59" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C59" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
@@ -2075,13 +2121,13 @@
     </row>
     <row r="60">
       <c r="A60" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B60" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C60" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
@@ -2108,17 +2154,17 @@
     </row>
     <row r="61">
       <c r="A61" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B61" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C61" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x3</t>
+          <t xml:space="preserve">P0v3 x2</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -2127,27 +2173,27 @@
         </is>
       </c>
       <c r="F61" s="12">
+        <v>3</v>
+      </c>
+      <c r="G61" s="12">
         <v>4</v>
       </c>
-      <c r="G61" s="12">
-        <v>5</v>
-      </c>
       <c r="H61" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I61" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B62" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C62" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
@@ -2174,17 +2220,17 @@
     </row>
     <row r="63">
       <c r="A63" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B63" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C63" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x4</t>
+          <t xml:space="preserve">P0v3 x3</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2193,13 +2239,13 @@
         </is>
       </c>
       <c r="F63" s="12">
+        <v>4</v>
+      </c>
+      <c r="G63" s="12">
         <v>5</v>
       </c>
-      <c r="G63" s="12">
-        <v>6</v>
-      </c>
       <c r="H63" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I63" s="12">
         <v>2</v>
@@ -2207,13 +2253,13 @@
     </row>
     <row r="64">
       <c r="A64" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B64" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C64" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
@@ -2240,13 +2286,13 @@
     </row>
     <row r="65">
       <c r="A65" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B65" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C65" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
@@ -2273,17 +2319,17 @@
     </row>
     <row r="66">
       <c r="A66" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B66" s="4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="C66" s="4">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x5</t>
+          <t xml:space="preserve">P0v3 x4</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2292,13 +2338,13 @@
         </is>
       </c>
       <c r="F66" s="12">
+        <v>5</v>
+      </c>
+      <c r="G66" s="12">
         <v>6</v>
       </c>
-      <c r="G66" s="12">
-        <v>7</v>
-      </c>
       <c r="H66" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I66" s="12">
         <v>2</v>
@@ -2306,13 +2352,13 @@
     </row>
     <row r="67">
       <c r="A67" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B67" s="4">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="C67" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
@@ -2339,13 +2385,13 @@
     </row>
     <row r="68">
       <c r="A68" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B68" s="4">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="C68" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
@@ -2372,13 +2418,13 @@
     </row>
     <row r="69">
       <c r="A69" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B69" s="4">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="C69" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
@@ -2400,18 +2446,18 @@
         <v>24</v>
       </c>
       <c r="I69" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B70" s="4">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="C70" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
@@ -2438,17 +2484,17 @@
     </row>
     <row r="71">
       <c r="A71" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="C71" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x6</t>
+          <t xml:space="preserve">P0v3 x5</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -2457,13 +2503,13 @@
         </is>
       </c>
       <c r="F71" s="12">
+        <v>6</v>
+      </c>
+      <c r="G71" s="12">
         <v>7</v>
       </c>
-      <c r="G71" s="12">
-        <v>8</v>
-      </c>
       <c r="H71" s="12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I71" s="12">
         <v>3</v>
@@ -2471,13 +2517,13 @@
     </row>
     <row r="72">
       <c r="A72" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B72" s="4">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="C72" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
@@ -2504,13 +2550,13 @@
     </row>
     <row r="73">
       <c r="A73" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B73" s="4">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="C73" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
@@ -2537,13 +2583,13 @@
     </row>
     <row r="74">
       <c r="A74" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B74" s="4">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="C74" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
@@ -2570,13 +2616,13 @@
     </row>
     <row r="75">
       <c r="A75" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B75" s="4">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="C75" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
@@ -2603,13 +2649,13 @@
     </row>
     <row r="76">
       <c r="A76" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B76" s="4">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="C76" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
@@ -2636,13 +2682,13 @@
     </row>
     <row r="77">
       <c r="A77" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B77" s="4">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="C77" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
@@ -2669,17 +2715,17 @@
     </row>
     <row r="78">
       <c r="A78" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B78" s="4">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="C78" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x7</t>
+          <t xml:space="preserve">P0v3 x6</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -2688,27 +2734,27 @@
         </is>
       </c>
       <c r="F78" s="12">
+        <v>7</v>
+      </c>
+      <c r="G78" s="12">
         <v>8</v>
       </c>
-      <c r="G78" s="12">
-        <v>9</v>
-      </c>
       <c r="H78" s="12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I78" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B79" s="4">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="C79" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
@@ -2735,13 +2781,13 @@
     </row>
     <row r="80">
       <c r="A80" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B80" s="4">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="C80" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
@@ -2768,13 +2814,13 @@
     </row>
     <row r="81">
       <c r="A81" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B81" s="4">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="C81" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
@@ -2801,13 +2847,13 @@
     </row>
     <row r="82">
       <c r="A82" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B82" s="4">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="C82" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
@@ -2834,13 +2880,13 @@
     </row>
     <row r="83">
       <c r="A83" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B83" s="4">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="C83" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
@@ -2867,13 +2913,13 @@
     </row>
     <row r="84">
       <c r="A84" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B84" s="4">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="C84" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
@@ -2900,17 +2946,17 @@
     </row>
     <row r="85">
       <c r="A85" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B85" s="4">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="C85" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x8</t>
+          <t xml:space="preserve">P0v3 x7</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -2919,13 +2965,13 @@
         </is>
       </c>
       <c r="F85" s="12">
+        <v>8</v>
+      </c>
+      <c r="G85" s="12">
         <v>9</v>
       </c>
-      <c r="G85" s="12">
-        <v>10</v>
-      </c>
       <c r="H85" s="12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I85" s="12">
         <v>4</v>
@@ -2933,13 +2979,13 @@
     </row>
     <row r="86">
       <c r="A86" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B86" s="4">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="C86" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
@@ -2961,18 +3007,18 @@
         <v>36</v>
       </c>
       <c r="I86" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B87" s="4">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="C87" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
@@ -2999,13 +3045,13 @@
     </row>
     <row r="88">
       <c r="A88" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B88" s="4">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="C88" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
@@ -3032,13 +3078,13 @@
     </row>
     <row r="89">
       <c r="A89" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B89" s="4">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="C89" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
@@ -3065,13 +3111,13 @@
     </row>
     <row r="90">
       <c r="A90" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B90" s="4">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="C90" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
@@ -3098,17 +3144,17 @@
     </row>
     <row r="91">
       <c r="A91" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B91" s="4">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="C91" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x9</t>
+          <t xml:space="preserve">P0v3 x8</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -3117,13 +3163,13 @@
         </is>
       </c>
       <c r="F91" s="12">
+        <v>9</v>
+      </c>
+      <c r="G91" s="12">
         <v>10</v>
       </c>
-      <c r="G91" s="12">
-        <v>11</v>
-      </c>
       <c r="H91" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I91" s="12">
         <v>5</v>
@@ -3131,13 +3177,13 @@
     </row>
     <row r="92">
       <c r="A92" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B92" s="4">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="C92" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
@@ -3164,13 +3210,13 @@
     </row>
     <row r="93">
       <c r="A93" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B93" s="4">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="C93" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
@@ -3197,13 +3243,13 @@
     </row>
     <row r="94">
       <c r="A94" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B94" s="4">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="C94" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
@@ -3230,13 +3276,13 @@
     </row>
     <row r="95">
       <c r="A95" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B95" s="4">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="C95" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
@@ -3258,18 +3304,18 @@
         <v>40</v>
       </c>
       <c r="I95" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B96" s="4">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="C96" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
@@ -3278,7 +3324,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F96" s="12">
@@ -3288,7 +3334,7 @@
         <v>11</v>
       </c>
       <c r="H96" s="12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I96" s="12">
         <v>6</v>
@@ -3296,13 +3342,13 @@
     </row>
     <row r="97">
       <c r="A97" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B97" s="4">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="C97" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
@@ -3329,17 +3375,17 @@
     </row>
     <row r="98">
       <c r="A98" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B98" s="4">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="C98" s="4">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x10</t>
+          <t xml:space="preserve">P0v3 x9</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -3348,134 +3394,134 @@
         </is>
       </c>
       <c r="F98" s="12">
+        <v>10</v>
+      </c>
+      <c r="G98" s="12">
         <v>11</v>
       </c>
-      <c r="G98" s="12">
-        <v>12</v>
-      </c>
       <c r="H98" s="12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I98" s="12">
         <v>6</v>
       </c>
     </row>
-    <row r="99" ht="10" customHeight="1"/>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="9">
+        <v>840</v>
+      </c>
+      <c r="B99" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="C99" s="4">
+        <v>29</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0v3 x10</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F99" s="12">
+        <v>11</v>
+      </c>
+      <c r="G99" s="12">
+        <v>12</v>
+      </c>
+      <c r="H99" s="12">
+        <v>48</v>
+      </c>
+      <c r="I99" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 250 Code Inspector users</t>
         </is>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-    </row>
-    <row r="101" ht="16.2" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" ht="16.2" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 250 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9">
-        <v>20</v>
-      </c>
-      <c r="B103" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C103" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0v3 x1</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F103" s="12">
-        <v>2</v>
-      </c>
-      <c r="G103" s="12">
-        <v>3</v>
-      </c>
-      <c r="H103" s="12">
-        <v>8</v>
-      </c>
-      <c r="I103" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B104" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C104" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x2</t>
+          <t xml:space="preserve">P0v3 x1</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -3484,13 +3530,13 @@
         </is>
       </c>
       <c r="F104" s="12">
+        <v>2</v>
+      </c>
+      <c r="G104" s="12">
         <v>3</v>
       </c>
-      <c r="G104" s="12">
-        <v>4</v>
-      </c>
       <c r="H104" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I104" s="12">
         <v>1</v>
@@ -3498,13 +3544,13 @@
     </row>
     <row r="105">
       <c r="A105" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B105" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C105" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
@@ -3531,13 +3577,13 @@
     </row>
     <row r="106">
       <c r="A106" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B106" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C106" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
@@ -3564,17 +3610,17 @@
     </row>
     <row r="107">
       <c r="A107" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B107" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C107" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x3</t>
+          <t xml:space="preserve">P0v3 x2</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -3583,27 +3629,27 @@
         </is>
       </c>
       <c r="F107" s="12">
+        <v>3</v>
+      </c>
+      <c r="G107" s="12">
         <v>4</v>
       </c>
-      <c r="G107" s="12">
-        <v>5</v>
-      </c>
       <c r="H107" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I107" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B108" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C108" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
@@ -3630,17 +3676,17 @@
     </row>
     <row r="109">
       <c r="A109" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B109" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C109" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x4</t>
+          <t xml:space="preserve">P0v3 x3</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -3649,13 +3695,13 @@
         </is>
       </c>
       <c r="F109" s="12">
+        <v>4</v>
+      </c>
+      <c r="G109" s="12">
         <v>5</v>
       </c>
-      <c r="G109" s="12">
-        <v>6</v>
-      </c>
       <c r="H109" s="12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I109" s="12">
         <v>2</v>
@@ -3663,13 +3709,13 @@
     </row>
     <row r="110">
       <c r="A110" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B110" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C110" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
@@ -3696,13 +3742,13 @@
     </row>
     <row r="111">
       <c r="A111" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B111" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C111" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
@@ -3729,17 +3775,17 @@
     </row>
     <row r="112">
       <c r="A112" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B112" s="4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="C112" s="4">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x5</t>
+          <t xml:space="preserve">P0v3 x4</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -3748,13 +3794,13 @@
         </is>
       </c>
       <c r="F112" s="12">
+        <v>5</v>
+      </c>
+      <c r="G112" s="12">
         <v>6</v>
       </c>
-      <c r="G112" s="12">
-        <v>7</v>
-      </c>
       <c r="H112" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I112" s="12">
         <v>2</v>
@@ -3762,13 +3808,13 @@
     </row>
     <row r="113">
       <c r="A113" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B113" s="4">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="C113" s="4">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
@@ -3795,17 +3841,17 @@
     </row>
     <row r="114">
       <c r="A114" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B114" s="4">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="C114" s="4">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x6</t>
+          <t xml:space="preserve">P0v3 x5</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -3814,13 +3860,13 @@
         </is>
       </c>
       <c r="F114" s="12">
+        <v>6</v>
+      </c>
+      <c r="G114" s="12">
         <v>7</v>
       </c>
-      <c r="G114" s="12">
-        <v>8</v>
-      </c>
       <c r="H114" s="12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I114" s="12">
         <v>2</v>
@@ -3828,13 +3874,13 @@
     </row>
     <row r="115">
       <c r="A115" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B115" s="4">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="C115" s="4">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
@@ -3856,18 +3902,18 @@
         <v>28</v>
       </c>
       <c r="I115" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B116" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C116" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
@@ -3894,13 +3940,13 @@
     </row>
     <row r="117">
       <c r="A117" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B117" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C117" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
@@ -3927,13 +3973,13 @@
     </row>
     <row r="118">
       <c r="A118" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B118" s="4">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="C118" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
@@ -3960,13 +4006,13 @@
     </row>
     <row r="119">
       <c r="A119" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B119" s="4">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="C119" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
@@ -3993,17 +4039,17 @@
     </row>
     <row r="120">
       <c r="A120" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B120" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C120" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x7</t>
+          <t xml:space="preserve">P0v3 x6</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -4012,13 +4058,13 @@
         </is>
       </c>
       <c r="F120" s="12">
+        <v>7</v>
+      </c>
+      <c r="G120" s="12">
         <v>8</v>
       </c>
-      <c r="G120" s="12">
-        <v>9</v>
-      </c>
       <c r="H120" s="12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I120" s="12">
         <v>3</v>
@@ -4026,13 +4072,13 @@
     </row>
     <row r="121">
       <c r="A121" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B121" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C121" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
@@ -4059,13 +4105,13 @@
     </row>
     <row r="122">
       <c r="A122" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B122" s="4">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="C122" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
@@ -4092,13 +4138,13 @@
     </row>
     <row r="123">
       <c r="A123" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B123" s="4">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="C123" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
@@ -4125,13 +4171,13 @@
     </row>
     <row r="124">
       <c r="A124" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B124" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C124" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
@@ -4153,18 +4199,18 @@
         <v>32</v>
       </c>
       <c r="I124" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B125" s="4">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="C125" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
@@ -4191,13 +4237,13 @@
     </row>
     <row r="126">
       <c r="A126" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B126" s="4">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="C126" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
@@ -4224,17 +4270,17 @@
     </row>
     <row r="127">
       <c r="A127" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B127" s="4">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="C127" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x8</t>
+          <t xml:space="preserve">P0v3 x7</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -4243,13 +4289,13 @@
         </is>
       </c>
       <c r="F127" s="12">
+        <v>8</v>
+      </c>
+      <c r="G127" s="12">
         <v>9</v>
       </c>
-      <c r="G127" s="12">
-        <v>10</v>
-      </c>
       <c r="H127" s="12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I127" s="12">
         <v>4</v>
@@ -4257,13 +4303,13 @@
     </row>
     <row r="128">
       <c r="A128" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B128" s="4">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="C128" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
@@ -4290,13 +4336,13 @@
     </row>
     <row r="129">
       <c r="A129" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B129" s="4">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="C129" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
@@ -4323,13 +4369,13 @@
     </row>
     <row r="130">
       <c r="A130" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B130" s="4">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="C130" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
@@ -4356,13 +4402,13 @@
     </row>
     <row r="131">
       <c r="A131" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B131" s="4">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="C131" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
@@ -4389,13 +4435,13 @@
     </row>
     <row r="132">
       <c r="A132" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B132" s="4">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="C132" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
@@ -4417,22 +4463,22 @@
         <v>36</v>
       </c>
       <c r="I132" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B133" s="4">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="C133" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x9</t>
+          <t xml:space="preserve">P0v3 x8</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -4441,13 +4487,13 @@
         </is>
       </c>
       <c r="F133" s="12">
+        <v>9</v>
+      </c>
+      <c r="G133" s="12">
         <v>10</v>
       </c>
-      <c r="G133" s="12">
-        <v>11</v>
-      </c>
       <c r="H133" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I133" s="12">
         <v>5</v>
@@ -4455,13 +4501,13 @@
     </row>
     <row r="134">
       <c r="A134" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B134" s="4">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="C134" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
@@ -4488,13 +4534,13 @@
     </row>
     <row r="135">
       <c r="A135" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B135" s="4">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="C135" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
@@ -4521,13 +4567,13 @@
     </row>
     <row r="136">
       <c r="A136" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B136" s="4">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="C136" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
@@ -4554,13 +4600,13 @@
     </row>
     <row r="137">
       <c r="A137" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B137" s="4">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="C137" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
@@ -4587,13 +4633,13 @@
     </row>
     <row r="138">
       <c r="A138" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B138" s="4">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="C138" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
@@ -4620,13 +4666,13 @@
     </row>
     <row r="139">
       <c r="A139" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B139" s="4">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="C139" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
@@ -4653,17 +4699,17 @@
     </row>
     <row r="140">
       <c r="A140" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B140" s="4">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="C140" s="4">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0v3 x10</t>
+          <t xml:space="preserve">P0v3 x9</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -4672,13 +4718,13 @@
         </is>
       </c>
       <c r="F140" s="12">
+        <v>10</v>
+      </c>
+      <c r="G140" s="12">
         <v>11</v>
       </c>
-      <c r="G140" s="12">
-        <v>12</v>
-      </c>
       <c r="H140" s="12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I140" s="12">
         <v>5</v>
@@ -4686,13 +4732,13 @@
     </row>
     <row r="141">
       <c r="A141" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B141" s="4">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="C141" s="4">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
@@ -4714,18 +4760,18 @@
         <v>44</v>
       </c>
       <c r="I141" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B142" s="4">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="C142" s="4">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
@@ -4734,7 +4780,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F142" s="12">
@@ -4744,7 +4790,7 @@
         <v>12</v>
       </c>
       <c r="H142" s="12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I142" s="12">
         <v>6</v>
@@ -4752,13 +4798,13 @@
     </row>
     <row r="143">
       <c r="A143" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B143" s="4">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="C143" s="4">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
@@ -4785,13 +4831,13 @@
     </row>
     <row r="144">
       <c r="A144" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B144" s="4">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="C144" s="4">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
@@ -4816,18 +4862,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" ht="10" customHeight="1"/>
+    <row r="145">
+      <c r="A145" s="9">
+        <v>840</v>
+      </c>
+      <c r="B145" s="4">
+        <v>22.9</v>
+      </c>
+      <c r="C145" s="4">
+        <v>31</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0v3 x10</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F145" s="12">
+        <v>11</v>
+      </c>
+      <c r="G145" s="12">
+        <v>12</v>
+      </c>
+      <c r="H145" s="12">
+        <v>48</v>
+      </c>
+      <c r="I145" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" ht="10" customHeight="1"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A102:I102"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -4878,129 +4958,103 @@
     <row r="5" ht="42.6" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Jobs at once" - searches and photo scans in flight at the SAME INSTANT, at the busiest moment of the busiest day. Not jobs per day, and not people signed in. A job holds a CPU core for only a second or two, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="29.4" customHeight="1">
+          <t xml:space="preserve">"Jobs at once" - searches and photo scans running at the SAME MOMENT, averaged across the busiest hour. Not jobs per day, and not people signed in. A Compass search holds a CPU core for about 12 seconds and an Inspector scan about 55, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55.8" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">A value below 1 is normal and is NOT a fraction of a machine. 0.5 means a job is in progress about half the busy hour and nothing is running the rest of it. Every option starts at one machine regardless; this figure says how hard that machine is worked. It is an average, so brief moments with two or three jobs at once still occur - that is what the headroom is for. Full worked example on the Read Me tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29.4" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">"Machines to buy" - web servers plus the index server, or a single server carrying both at small scale. Where the index host reads "on web server" the count is 1, and both workloads share it.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass only</t>
         </is>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" ht="16.2" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" ht="16.2" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Every seat runs 15–20 Code Compass searches per working day.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on web server</t>
-        </is>
-      </c>
-      <c r="F11" s="12">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12">
-        <v>2</v>
-      </c>
-      <c r="H11" s="12">
-        <v>4</v>
-      </c>
-      <c r="I11" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
@@ -5027,13 +5081,13 @@
     </row>
     <row r="13">
       <c r="A13" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
@@ -5060,13 +5114,13 @@
     </row>
     <row r="14">
       <c r="A14" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B14" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="C14" s="4">
         <v>1.5</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
@@ -5093,13 +5147,13 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B15" s="4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="4">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
@@ -5121,18 +5175,18 @@
         <v>4</v>
       </c>
       <c r="I15" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="C16" s="4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -5159,13 +5213,13 @@
     </row>
     <row r="17">
       <c r="A17" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B17" s="4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="C17" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -5192,13 +5246,13 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B18" s="4">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C18" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
@@ -5225,13 +5279,13 @@
     </row>
     <row r="19">
       <c r="A19" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B19" s="4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
@@ -5258,17 +5312,17 @@
     </row>
     <row r="20">
       <c r="A20" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B20" s="4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="C20" s="4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -5283,7 +5337,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12">
         <v>2</v>
@@ -5291,13 +5345,13 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B21" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C21" s="4">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
@@ -5324,17 +5378,17 @@
     </row>
     <row r="22">
       <c r="A22" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B22" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="C22" s="4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4s_v2 x1</t>
+          <t xml:space="preserve">B2s_v2 x1</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -5346,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12">
         <v>2</v>
@@ -5357,13 +5411,13 @@
     </row>
     <row r="23">
       <c r="A23" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B23" s="4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C23" s="4">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
@@ -5385,18 +5439,18 @@
         <v>16</v>
       </c>
       <c r="I23" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B24" s="4">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="C24" s="4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
@@ -5423,13 +5477,13 @@
     </row>
     <row r="25">
       <c r="A25" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B25" s="4">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="C25" s="4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
@@ -5456,13 +5510,13 @@
     </row>
     <row r="26">
       <c r="A26" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B26" s="4">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="C26" s="4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
@@ -5489,13 +5543,13 @@
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B27" s="4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
@@ -5522,13 +5576,13 @@
     </row>
     <row r="28">
       <c r="A28" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B28" s="4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="C28" s="4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
@@ -5555,13 +5609,13 @@
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B29" s="4">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="C29" s="4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
@@ -5588,13 +5642,13 @@
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="C30" s="4">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
@@ -5621,13 +5675,13 @@
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B31" s="4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="C31" s="4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
@@ -5654,13 +5708,13 @@
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B32" s="4">
-        <v>8.3</v>
+        <v>7.9</v>
       </c>
       <c r="C32" s="4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
@@ -5682,18 +5736,18 @@
         <v>16</v>
       </c>
       <c r="I32" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B33" s="4">
-        <v>8.6</v>
+        <v>8.3</v>
       </c>
       <c r="C33" s="4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
@@ -5719,80 +5773,80 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8">
+      <c r="A34" s="9">
+        <v>460</v>
+      </c>
+      <c r="B34" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="C34" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B4s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on web server</t>
+        </is>
+      </c>
+      <c r="F34" s="12">
+        <v>1</v>
+      </c>
+      <c r="G34" s="12">
+        <v>4</v>
+      </c>
+      <c r="H34" s="12">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8">
         <v>480</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B35" s="4">
         <v>9</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C35" s="4">
         <v>12</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">B4s_v2 x1</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F34" s="13">
-        <v>2</v>
-      </c>
-      <c r="G34" s="13">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2ls_v2 x1</t>
+        </is>
+      </c>
+      <c r="F35" s="13">
+        <v>2</v>
+      </c>
+      <c r="G35" s="13">
         <v>6</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H35" s="13">
         <v>20</v>
       </c>
-      <c r="I34" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9">
-        <v>500</v>
-      </c>
-      <c r="B35" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="C35" s="4">
-        <v>12.5</v>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B8s_v2 x1</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F35" s="12">
-        <v>2</v>
-      </c>
-      <c r="G35" s="12">
-        <v>10</v>
-      </c>
-      <c r="H35" s="12">
-        <v>36</v>
-      </c>
-      <c r="I35" s="12">
+      <c r="I35" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B36" s="4">
-        <v>9.8</v>
+        <v>9.4</v>
       </c>
       <c r="C36" s="4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
@@ -5819,13 +5873,13 @@
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B37" s="4">
-        <v>10.1</v>
+        <v>9.8</v>
       </c>
       <c r="C37" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
@@ -5852,13 +5906,13 @@
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B38" s="4">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="C38" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
@@ -5885,13 +5939,13 @@
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B39" s="4">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="C39" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
@@ -5918,13 +5972,13 @@
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B40" s="4">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="C40" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
@@ -5946,18 +6000,18 @@
         <v>36</v>
       </c>
       <c r="I40" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B41" s="4">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="C41" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
@@ -5984,13 +6038,13 @@
     </row>
     <row r="42">
       <c r="A42" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B42" s="4">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="C42" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
@@ -6017,13 +6071,13 @@
     </row>
     <row r="43">
       <c r="A43" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B43" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C43" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
@@ -6050,13 +6104,13 @@
     </row>
     <row r="44">
       <c r="A44" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B44" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C44" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
@@ -6083,13 +6137,13 @@
     </row>
     <row r="45">
       <c r="A45" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B45" s="4">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="C45" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -6116,13 +6170,13 @@
     </row>
     <row r="46">
       <c r="A46" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B46" s="4">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="C46" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
@@ -6149,13 +6203,13 @@
     </row>
     <row r="47">
       <c r="A47" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B47" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C47" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
@@ -6182,13 +6236,13 @@
     </row>
     <row r="48">
       <c r="A48" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B48" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C48" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
@@ -6215,13 +6269,13 @@
     </row>
     <row r="49">
       <c r="A49" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B49" s="4">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="C49" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
@@ -6243,18 +6297,18 @@
         <v>36</v>
       </c>
       <c r="I49" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B50" s="4">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="C50" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
@@ -6263,7 +6317,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F50" s="12">
@@ -6273,7 +6327,7 @@
         <v>10</v>
       </c>
       <c r="H50" s="12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I50" s="12">
         <v>6</v>
@@ -6281,13 +6335,13 @@
     </row>
     <row r="51">
       <c r="A51" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B51" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C51" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
@@ -6314,13 +6368,13 @@
     </row>
     <row r="52">
       <c r="A52" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B52" s="4">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="C52" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
@@ -6345,118 +6399,118 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" ht="10" customHeight="1"/>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9">
+        <v>840</v>
+      </c>
+      <c r="B53" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="C53" s="4">
+        <v>21</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B8s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F53" s="12">
+        <v>2</v>
+      </c>
+      <c r="G53" s="12">
+        <v>10</v>
+      </c>
+      <c r="H53" s="12">
+        <v>40</v>
+      </c>
+      <c r="I53" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" ht="10" customHeight="1"/>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 200 Code Inspector users</t>
         </is>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" ht="16.2" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" ht="16.2" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 200 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9">
-        <v>20</v>
-      </c>
-      <c r="B57" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C57" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on web server</t>
-        </is>
-      </c>
-      <c r="F57" s="12">
-        <v>1</v>
-      </c>
-      <c r="G57" s="12">
-        <v>2</v>
-      </c>
-      <c r="H57" s="12">
-        <v>4</v>
-      </c>
-      <c r="I57" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B58" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C58" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
@@ -6483,13 +6537,13 @@
     </row>
     <row r="59">
       <c r="A59" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B59" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C59" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
@@ -6516,13 +6570,13 @@
     </row>
     <row r="60">
       <c r="A60" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B60" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C60" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
@@ -6549,17 +6603,17 @@
     </row>
     <row r="61">
       <c r="A61" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B61" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C61" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -6571,24 +6625,24 @@
         <v>1</v>
       </c>
       <c r="G61" s="12">
+        <v>2</v>
+      </c>
+      <c r="H61" s="12">
         <v>4</v>
       </c>
-      <c r="H61" s="12">
-        <v>16</v>
-      </c>
       <c r="I61" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B62" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C62" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
@@ -6615,13 +6669,13 @@
     </row>
     <row r="63">
       <c r="A63" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B63" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C63" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
@@ -6648,13 +6702,13 @@
     </row>
     <row r="64">
       <c r="A64" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B64" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C64" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
@@ -6681,13 +6735,13 @@
     </row>
     <row r="65">
       <c r="A65" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B65" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C65" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
@@ -6713,80 +6767,80 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8">
+      <c r="A66" s="9">
+        <v>180</v>
+      </c>
+      <c r="B66" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="C66" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B4s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on web server</t>
+        </is>
+      </c>
+      <c r="F66" s="12">
+        <v>1</v>
+      </c>
+      <c r="G66" s="12">
+        <v>4</v>
+      </c>
+      <c r="H66" s="12">
+        <v>16</v>
+      </c>
+      <c r="I66" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8">
         <v>200</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B67" s="4">
         <v>9.5</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C67" s="4">
         <v>13</v>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">B8s_v2 x1</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F66" s="13">
-        <v>2</v>
-      </c>
-      <c r="G66" s="13">
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2ls_v2 x1</t>
+        </is>
+      </c>
+      <c r="F67" s="13">
+        <v>2</v>
+      </c>
+      <c r="G67" s="13">
         <v>10</v>
       </c>
-      <c r="H66" s="13">
+      <c r="H67" s="13">
         <v>36</v>
       </c>
-      <c r="I66" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9">
-        <v>220</v>
-      </c>
-      <c r="B67" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="C67" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B8s_v2 x1</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F67" s="12">
-        <v>2</v>
-      </c>
-      <c r="G67" s="12">
-        <v>10</v>
-      </c>
-      <c r="H67" s="12">
-        <v>36</v>
-      </c>
-      <c r="I67" s="12">
+      <c r="I67" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B68" s="4">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="C68" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
@@ -6813,13 +6867,13 @@
     </row>
     <row r="69">
       <c r="A69" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B69" s="4">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="C69" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
@@ -6841,18 +6895,18 @@
         <v>36</v>
       </c>
       <c r="I69" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B70" s="4">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="C70" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
@@ -6879,13 +6933,13 @@
     </row>
     <row r="71">
       <c r="A71" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="C71" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
@@ -6912,13 +6966,13 @@
     </row>
     <row r="72">
       <c r="A72" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B72" s="4">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="C72" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
@@ -6945,13 +6999,13 @@
     </row>
     <row r="73">
       <c r="A73" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B73" s="4">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="C73" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
@@ -6978,13 +7032,13 @@
     </row>
     <row r="74">
       <c r="A74" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B74" s="4">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="C74" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
@@ -7011,13 +7065,13 @@
     </row>
     <row r="75">
       <c r="A75" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B75" s="4">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="C75" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
@@ -7044,13 +7098,13 @@
     </row>
     <row r="76">
       <c r="A76" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B76" s="4">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="C76" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
@@ -7077,13 +7131,13 @@
     </row>
     <row r="77">
       <c r="A77" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B77" s="4">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="C77" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
@@ -7110,13 +7164,13 @@
     </row>
     <row r="78">
       <c r="A78" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B78" s="4">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="C78" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
@@ -7138,18 +7192,18 @@
         <v>36</v>
       </c>
       <c r="I78" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B79" s="4">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="C79" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
@@ -7176,13 +7230,13 @@
     </row>
     <row r="80">
       <c r="A80" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B80" s="4">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="C80" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
@@ -7209,13 +7263,13 @@
     </row>
     <row r="81">
       <c r="A81" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B81" s="4">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="C81" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
@@ -7242,13 +7296,13 @@
     </row>
     <row r="82">
       <c r="A82" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B82" s="4">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="C82" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
@@ -7275,13 +7329,13 @@
     </row>
     <row r="83">
       <c r="A83" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B83" s="4">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="C83" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
@@ -7308,13 +7362,13 @@
     </row>
     <row r="84">
       <c r="A84" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B84" s="4">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="C84" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
@@ -7341,13 +7395,13 @@
     </row>
     <row r="85">
       <c r="A85" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B85" s="4">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="C85" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
@@ -7374,13 +7428,13 @@
     </row>
     <row r="86">
       <c r="A86" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B86" s="4">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="C86" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
@@ -7402,18 +7456,18 @@
         <v>36</v>
       </c>
       <c r="I86" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B87" s="4">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="C87" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
@@ -7440,13 +7494,13 @@
     </row>
     <row r="88">
       <c r="A88" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B88" s="4">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="C88" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
@@ -7473,13 +7527,13 @@
     </row>
     <row r="89">
       <c r="A89" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B89" s="4">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="C89" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
@@ -7506,13 +7560,13 @@
     </row>
     <row r="90">
       <c r="A90" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B90" s="4">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="C90" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
@@ -7539,17 +7593,17 @@
     </row>
     <row r="91">
       <c r="A91" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B91" s="4">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="C91" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B16s_v2 x1</t>
+          <t xml:space="preserve">B8s_v2 x1</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -7561,10 +7615,10 @@
         <v>2</v>
       </c>
       <c r="G91" s="12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H91" s="12">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I91" s="12">
         <v>5</v>
@@ -7572,13 +7626,13 @@
     </row>
     <row r="92">
       <c r="A92" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B92" s="4">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="C92" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
@@ -7605,13 +7659,13 @@
     </row>
     <row r="93">
       <c r="A93" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B93" s="4">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="C93" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
@@ -7638,13 +7692,13 @@
     </row>
     <row r="94">
       <c r="A94" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B94" s="4">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="C94" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
@@ -7671,13 +7725,13 @@
     </row>
     <row r="95">
       <c r="A95" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B95" s="4">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="C95" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
@@ -7699,18 +7753,18 @@
         <v>68</v>
       </c>
       <c r="I95" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B96" s="4">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="C96" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
@@ -7719,7 +7773,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F96" s="12">
@@ -7729,7 +7783,7 @@
         <v>18</v>
       </c>
       <c r="H96" s="12">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I96" s="12">
         <v>6</v>
@@ -7737,13 +7791,13 @@
     </row>
     <row r="97">
       <c r="A97" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B97" s="4">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="C97" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
@@ -7770,13 +7824,13 @@
     </row>
     <row r="98">
       <c r="A98" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B98" s="4">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="C98" s="4">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -7801,118 +7855,118 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" ht="10" customHeight="1"/>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="9">
+        <v>840</v>
+      </c>
+      <c r="B99" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="C99" s="4">
+        <v>29</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B16s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F99" s="12">
+        <v>2</v>
+      </c>
+      <c r="G99" s="12">
+        <v>18</v>
+      </c>
+      <c r="H99" s="12">
+        <v>72</v>
+      </c>
+      <c r="I99" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 250 Code Inspector users</t>
         </is>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-    </row>
-    <row r="101" ht="16.2" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" ht="16.2" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 250 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Web tier (size x how many)</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (web + index)</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total vCPU (all machines)</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Total RAM GB (all machines)</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index disk GB</t>
         </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9">
-        <v>20</v>
-      </c>
-      <c r="B103" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C103" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on web server</t>
-        </is>
-      </c>
-      <c r="F103" s="12">
-        <v>1</v>
-      </c>
-      <c r="G103" s="12">
-        <v>2</v>
-      </c>
-      <c r="H103" s="12">
-        <v>4</v>
-      </c>
-      <c r="I103" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B104" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C104" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
@@ -7939,13 +7993,13 @@
     </row>
     <row r="105">
       <c r="A105" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B105" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C105" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
@@ -7972,13 +8026,13 @@
     </row>
     <row r="106">
       <c r="A106" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B106" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C106" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
@@ -8005,17 +8059,17 @@
     </row>
     <row r="107">
       <c r="A107" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B107" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C107" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -8027,24 +8081,24 @@
         <v>1</v>
       </c>
       <c r="G107" s="12">
+        <v>2</v>
+      </c>
+      <c r="H107" s="12">
         <v>4</v>
       </c>
-      <c r="H107" s="12">
-        <v>16</v>
-      </c>
       <c r="I107" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B108" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C108" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
@@ -8071,13 +8125,13 @@
     </row>
     <row r="109">
       <c r="A109" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B109" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C109" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
@@ -8104,13 +8158,13 @@
     </row>
     <row r="110">
       <c r="A110" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B110" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C110" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
@@ -8137,13 +8191,13 @@
     </row>
     <row r="111">
       <c r="A111" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B111" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C111" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
@@ -8169,80 +8223,80 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8">
+      <c r="A112" s="9">
+        <v>180</v>
+      </c>
+      <c r="B112" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="C112" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B4s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on web server</t>
+        </is>
+      </c>
+      <c r="F112" s="12">
+        <v>1</v>
+      </c>
+      <c r="G112" s="12">
+        <v>4</v>
+      </c>
+      <c r="H112" s="12">
+        <v>16</v>
+      </c>
+      <c r="I112" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8">
         <v>200</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B113" s="4">
         <v>9.5</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C113" s="4">
         <v>13</v>
       </c>
-      <c r="D112" s="8" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">B8s_v2 x1</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F112" s="13">
-        <v>2</v>
-      </c>
-      <c r="G112" s="13">
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2ls_v2 x1</t>
+        </is>
+      </c>
+      <c r="F113" s="13">
+        <v>2</v>
+      </c>
+      <c r="G113" s="13">
         <v>10</v>
       </c>
-      <c r="H112" s="13">
+      <c r="H113" s="13">
         <v>36</v>
       </c>
-      <c r="I112" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9">
-        <v>220</v>
-      </c>
-      <c r="B113" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="C113" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B8s_v2 x1</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="F113" s="12">
-        <v>2</v>
-      </c>
-      <c r="G113" s="12">
-        <v>10</v>
-      </c>
-      <c r="H113" s="12">
-        <v>36</v>
-      </c>
-      <c r="I113" s="12">
+      <c r="I113" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B114" s="4">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="C114" s="4">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
@@ -8269,13 +8323,13 @@
     </row>
     <row r="115">
       <c r="A115" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B115" s="4">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="C115" s="4">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
@@ -8297,18 +8351,18 @@
         <v>36</v>
       </c>
       <c r="I115" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B116" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C116" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
@@ -8335,13 +8389,13 @@
     </row>
     <row r="117">
       <c r="A117" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B117" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C117" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
@@ -8368,13 +8422,13 @@
     </row>
     <row r="118">
       <c r="A118" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B118" s="4">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="C118" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
@@ -8401,13 +8455,13 @@
     </row>
     <row r="119">
       <c r="A119" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B119" s="4">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="C119" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
@@ -8434,13 +8488,13 @@
     </row>
     <row r="120">
       <c r="A120" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B120" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C120" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
@@ -8467,13 +8521,13 @@
     </row>
     <row r="121">
       <c r="A121" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B121" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C121" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
@@ -8500,13 +8554,13 @@
     </row>
     <row r="122">
       <c r="A122" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B122" s="4">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="C122" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
@@ -8533,13 +8587,13 @@
     </row>
     <row r="123">
       <c r="A123" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B123" s="4">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="C123" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
@@ -8566,13 +8620,13 @@
     </row>
     <row r="124">
       <c r="A124" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B124" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C124" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
@@ -8594,18 +8648,18 @@
         <v>36</v>
       </c>
       <c r="I124" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B125" s="4">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="C125" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
@@ -8632,13 +8686,13 @@
     </row>
     <row r="126">
       <c r="A126" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B126" s="4">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="C126" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
@@ -8665,13 +8719,13 @@
     </row>
     <row r="127">
       <c r="A127" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B127" s="4">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="C127" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
@@ -8698,13 +8752,13 @@
     </row>
     <row r="128">
       <c r="A128" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B128" s="4">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="C128" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
@@ -8731,13 +8785,13 @@
     </row>
     <row r="129">
       <c r="A129" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B129" s="4">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="C129" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
@@ -8764,13 +8818,13 @@
     </row>
     <row r="130">
       <c r="A130" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B130" s="4">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="C130" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
@@ -8797,13 +8851,13 @@
     </row>
     <row r="131">
       <c r="A131" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B131" s="4">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="C131" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
@@ -8830,13 +8884,13 @@
     </row>
     <row r="132">
       <c r="A132" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B132" s="4">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="C132" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
@@ -8858,22 +8912,22 @@
         <v>36</v>
       </c>
       <c r="I132" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B133" s="4">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="C133" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B16s_v2 x1</t>
+          <t xml:space="preserve">B8s_v2 x1</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -8885,10 +8939,10 @@
         <v>2</v>
       </c>
       <c r="G133" s="12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H133" s="12">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I133" s="12">
         <v>5</v>
@@ -8896,13 +8950,13 @@
     </row>
     <row r="134">
       <c r="A134" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B134" s="4">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="C134" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
@@ -8929,13 +8983,13 @@
     </row>
     <row r="135">
       <c r="A135" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B135" s="4">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="C135" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
@@ -8962,13 +9016,13 @@
     </row>
     <row r="136">
       <c r="A136" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B136" s="4">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="C136" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
@@ -8995,13 +9049,13 @@
     </row>
     <row r="137">
       <c r="A137" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B137" s="4">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="C137" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
@@ -9028,13 +9082,13 @@
     </row>
     <row r="138">
       <c r="A138" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B138" s="4">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="C138" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
@@ -9061,13 +9115,13 @@
     </row>
     <row r="139">
       <c r="A139" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B139" s="4">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="C139" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
@@ -9094,13 +9148,13 @@
     </row>
     <row r="140">
       <c r="A140" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B140" s="4">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="C140" s="4">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
@@ -9127,13 +9181,13 @@
     </row>
     <row r="141">
       <c r="A141" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B141" s="4">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="C141" s="4">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
@@ -9155,18 +9209,18 @@
         <v>68</v>
       </c>
       <c r="I141" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B142" s="4">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="C142" s="4">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
@@ -9175,7 +9229,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="F142" s="12">
@@ -9185,7 +9239,7 @@
         <v>18</v>
       </c>
       <c r="H142" s="12">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I142" s="12">
         <v>6</v>
@@ -9193,13 +9247,13 @@
     </row>
     <row r="143">
       <c r="A143" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B143" s="4">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="C143" s="4">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
@@ -9226,13 +9280,13 @@
     </row>
     <row r="144">
       <c r="A144" s="9">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B144" s="4">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="C144" s="4">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
@@ -9257,26 +9311,60 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" ht="10" customHeight="1"/>
-    <row r="146" ht="16.2" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="9">
+        <v>840</v>
+      </c>
+      <c r="B145" s="4">
+        <v>22.9</v>
+      </c>
+      <c r="C145" s="4">
+        <v>31</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B16s_v2 x1</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="F145" s="12">
+        <v>2</v>
+      </c>
+      <c r="G145" s="12">
+        <v>18</v>
+      </c>
+      <c r="H145" s="12">
+        <v>72</v>
+      </c>
+      <c r="I145" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" ht="10" customHeight="1"/>
+    <row r="147" ht="16.2" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaded rows: the search index moves onto its own machine here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A101:I101"/>
-    <mergeCell ref="A146:I146"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A147:I147"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -9327,127 +9415,103 @@
     <row r="5" ht="42.6" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Jobs at once" - searches and photo scans in flight at the SAME INSTANT, at the busiest moment of the busiest day. Not jobs per day, and not people signed in. A job holds a CPU core for only a second or two, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="29.4" customHeight="1">
+          <t xml:space="preserve">"Jobs at once" - searches and photo scans running at the SAME MOMENT, averaged across the busiest hour. Not jobs per day, and not people signed in. A Compass search holds a CPU core for about 12 seconds and an Inspector scan about 55, so this is what determines the hardware. Two columns because usage is a range; everything to the right is sized on the busy figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55.8" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">A value below 1 is normal and is NOT a fraction of a machine. 0.5 means a job is in progress about half the busy hour and nothing is running the rest of it. Every option starts at one machine regardless; this figure says how hard that machine is worked. It is an average, so brief moments with two or three jobs at once still occur - that is what the headroom is for. Full worked example on the Read Me tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29.4" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">"Machines to buy" - the index host ONLY. Replicas are not machines you provision: Container Apps starts and stops them as traffic moves, and bills by request. The peak replica column says how many run at the busiest moment, not what you order.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1"/>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass only</t>
         </is>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" ht="16.2" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" ht="16.2" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Every seat runs 15–20 Code Compass searches per working day.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Peak replicas (platform-managed)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Warm replicas</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">vCPU per replica</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">RAM GB per replica</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (index only)</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="12">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12">
-        <v>1</v>
-      </c>
-      <c r="F11" s="12">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12">
-        <v>2</v>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="I11" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -9472,13 +9536,13 @@
     </row>
     <row r="13">
       <c r="A13" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C13" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="12">
         <v>1</v>
@@ -9503,13 +9567,13 @@
     </row>
     <row r="14">
       <c r="A14" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B14" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="C14" s="4">
         <v>1.5</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -9534,13 +9598,13 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B15" s="4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="4">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
@@ -9565,13 +9629,13 @@
     </row>
     <row r="16">
       <c r="A16" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="C16" s="4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -9596,13 +9660,13 @@
     </row>
     <row r="17">
       <c r="A17" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B17" s="4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="C17" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="12">
         <v>1</v>
@@ -9627,13 +9691,13 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B18" s="4">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C18" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="12">
         <v>1</v>
@@ -9658,13 +9722,13 @@
     </row>
     <row r="19">
       <c r="A19" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B19" s="4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -9689,13 +9753,13 @@
     </row>
     <row r="20">
       <c r="A20" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B20" s="4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="C20" s="4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -9720,13 +9784,13 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B21" s="4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C21" s="4">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -9751,13 +9815,13 @@
     </row>
     <row r="22">
       <c r="A22" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B22" s="4">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="C22" s="4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -9782,13 +9846,13 @@
     </row>
     <row r="23">
       <c r="A23" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B23" s="4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C23" s="4">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -9813,13 +9877,13 @@
     </row>
     <row r="24">
       <c r="A24" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B24" s="4">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="C24" s="4">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
@@ -9844,13 +9908,13 @@
     </row>
     <row r="25">
       <c r="A25" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B25" s="4">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="C25" s="4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="12">
         <v>1</v>
@@ -9875,13 +9939,13 @@
     </row>
     <row r="26">
       <c r="A26" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B26" s="4">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="C26" s="4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D26" s="12">
         <v>1</v>
@@ -9906,13 +9970,13 @@
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B27" s="4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
@@ -9937,13 +10001,13 @@
     </row>
     <row r="28">
       <c r="A28" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B28" s="4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="C28" s="4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D28" s="12">
         <v>1</v>
@@ -9968,13 +10032,13 @@
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B29" s="4">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="C29" s="4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
@@ -9999,13 +10063,13 @@
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="C30" s="4">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
@@ -10030,13 +10094,13 @@
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B31" s="4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="C31" s="4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -10061,13 +10125,13 @@
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B32" s="4">
-        <v>8.3</v>
+        <v>7.9</v>
       </c>
       <c r="C32" s="4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -10092,13 +10156,13 @@
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B33" s="4">
-        <v>8.6</v>
+        <v>8.3</v>
       </c>
       <c r="C33" s="4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -10123,13 +10187,13 @@
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B34" s="4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="C34" s="4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -10154,13 +10218,13 @@
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B35" s="4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="C35" s="4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -10185,13 +10249,13 @@
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B36" s="4">
-        <v>9.8</v>
+        <v>9.4</v>
       </c>
       <c r="C36" s="4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -10216,13 +10280,13 @@
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B37" s="4">
-        <v>10.1</v>
+        <v>9.8</v>
       </c>
       <c r="C37" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -10247,13 +10311,13 @@
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B38" s="4">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="C38" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
@@ -10278,13 +10342,13 @@
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B39" s="4">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="C39" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -10309,13 +10373,13 @@
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B40" s="4">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="C40" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
@@ -10340,13 +10404,13 @@
     </row>
     <row r="41">
       <c r="A41" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B41" s="4">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="C41" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -10371,13 +10435,13 @@
     </row>
     <row r="42">
       <c r="A42" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B42" s="4">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="C42" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -10402,13 +10466,13 @@
     </row>
     <row r="43">
       <c r="A43" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B43" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C43" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -10433,13 +10497,13 @@
     </row>
     <row r="44">
       <c r="A44" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B44" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C44" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -10464,13 +10528,13 @@
     </row>
     <row r="45">
       <c r="A45" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B45" s="4">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="C45" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D45" s="12">
         <v>1</v>
@@ -10495,13 +10559,13 @@
     </row>
     <row r="46">
       <c r="A46" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B46" s="4">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="C46" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -10526,13 +10590,13 @@
     </row>
     <row r="47">
       <c r="A47" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B47" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C47" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -10557,13 +10621,13 @@
     </row>
     <row r="48">
       <c r="A48" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B48" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C48" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D48" s="12">
         <v>1</v>
@@ -10588,13 +10652,13 @@
     </row>
     <row r="49">
       <c r="A49" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B49" s="4">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="C49" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -10619,13 +10683,13 @@
     </row>
     <row r="50">
       <c r="A50" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B50" s="4">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="C50" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -10641,7 +10705,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="I50" s="12">
@@ -10650,13 +10714,13 @@
     </row>
     <row r="51">
       <c r="A51" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B51" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C51" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D51" s="12">
         <v>1</v>
@@ -10681,145 +10745,145 @@
     </row>
     <row r="52">
       <c r="A52" s="9">
+        <v>820</v>
+      </c>
+      <c r="B52" s="4">
+        <v>15.4</v>
+      </c>
+      <c r="C52" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="D52" s="12">
+        <v>1</v>
+      </c>
+      <c r="E52" s="12">
+        <v>1</v>
+      </c>
+      <c r="F52" s="12">
+        <v>1</v>
+      </c>
+      <c r="G52" s="12">
+        <v>2</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="I52" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9">
         <v>840</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B53" s="4">
         <v>15.8</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C53" s="4">
         <v>21</v>
       </c>
-      <c r="D52" s="12">
-        <v>1</v>
-      </c>
-      <c r="E52" s="12">
-        <v>1</v>
-      </c>
-      <c r="F52" s="12">
-        <v>1</v>
-      </c>
-      <c r="G52" s="12">
-        <v>2</v>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="D53" s="12">
+        <v>1</v>
+      </c>
+      <c r="E53" s="12">
+        <v>1</v>
+      </c>
+      <c r="F53" s="12">
+        <v>1</v>
+      </c>
+      <c r="G53" s="12">
+        <v>2</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">B2s_v2 x1</t>
         </is>
       </c>
-      <c r="I52" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" ht="10" customHeight="1"/>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="I53" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" ht="10" customHeight="1"/>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 200 Code Inspector users</t>
         </is>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" ht="16.2" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" ht="16.2" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 200 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Peak replicas (platform-managed)</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Warm replicas</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">vCPU per replica</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">RAM GB per replica</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (index only)</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9">
-        <v>20</v>
-      </c>
-      <c r="B57" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C57" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D57" s="12">
-        <v>1</v>
-      </c>
-      <c r="E57" s="12">
-        <v>1</v>
-      </c>
-      <c r="F57" s="12">
-        <v>1</v>
-      </c>
-      <c r="G57" s="12">
-        <v>2</v>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="I57" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B58" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C58" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -10844,13 +10908,13 @@
     </row>
     <row r="59">
       <c r="A59" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B59" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C59" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -10875,13 +10939,13 @@
     </row>
     <row r="60">
       <c r="A60" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B60" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C60" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
@@ -10906,13 +10970,13 @@
     </row>
     <row r="61">
       <c r="A61" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B61" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C61" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
@@ -10937,13 +11001,13 @@
     </row>
     <row r="62">
       <c r="A62" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B62" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C62" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D62" s="12">
         <v>1</v>
@@ -10968,13 +11032,13 @@
     </row>
     <row r="63">
       <c r="A63" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B63" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C63" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -10999,13 +11063,13 @@
     </row>
     <row r="64">
       <c r="A64" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B64" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C64" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D64" s="12">
         <v>1</v>
@@ -11030,13 +11094,13 @@
     </row>
     <row r="65">
       <c r="A65" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B65" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C65" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -11061,13 +11125,13 @@
     </row>
     <row r="66">
       <c r="A66" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B66" s="4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="C66" s="4">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
@@ -11092,13 +11156,13 @@
     </row>
     <row r="67">
       <c r="A67" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B67" s="4">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="C67" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D67" s="12">
         <v>1</v>
@@ -11123,13 +11187,13 @@
     </row>
     <row r="68">
       <c r="A68" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B68" s="4">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="C68" s="4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D68" s="12">
         <v>1</v>
@@ -11154,13 +11218,13 @@
     </row>
     <row r="69">
       <c r="A69" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B69" s="4">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="C69" s="4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="D69" s="12">
         <v>1</v>
@@ -11185,13 +11249,13 @@
     </row>
     <row r="70">
       <c r="A70" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B70" s="4">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="C70" s="4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
@@ -11216,13 +11280,13 @@
     </row>
     <row r="71">
       <c r="A71" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B71" s="4">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="C71" s="4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D71" s="12">
         <v>1</v>
@@ -11247,13 +11311,13 @@
     </row>
     <row r="72">
       <c r="A72" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B72" s="4">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="C72" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D72" s="12">
         <v>1</v>
@@ -11278,13 +11342,13 @@
     </row>
     <row r="73">
       <c r="A73" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B73" s="4">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="C73" s="4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D73" s="12">
         <v>1</v>
@@ -11309,13 +11373,13 @@
     </row>
     <row r="74">
       <c r="A74" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B74" s="4">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="C74" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D74" s="12">
         <v>1</v>
@@ -11340,13 +11404,13 @@
     </row>
     <row r="75">
       <c r="A75" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B75" s="4">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="C75" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D75" s="12">
         <v>1</v>
@@ -11371,13 +11435,13 @@
     </row>
     <row r="76">
       <c r="A76" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B76" s="4">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="C76" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D76" s="12">
         <v>1</v>
@@ -11402,13 +11466,13 @@
     </row>
     <row r="77">
       <c r="A77" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B77" s="4">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="C77" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D77" s="12">
         <v>1</v>
@@ -11433,13 +11497,13 @@
     </row>
     <row r="78">
       <c r="A78" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B78" s="4">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="C78" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D78" s="12">
         <v>1</v>
@@ -11464,13 +11528,13 @@
     </row>
     <row r="79">
       <c r="A79" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B79" s="4">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="C79" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D79" s="12">
         <v>1</v>
@@ -11495,13 +11559,13 @@
     </row>
     <row r="80">
       <c r="A80" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B80" s="4">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="C80" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D80" s="12">
         <v>1</v>
@@ -11526,13 +11590,13 @@
     </row>
     <row r="81">
       <c r="A81" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B81" s="4">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="C81" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D81" s="12">
         <v>1</v>
@@ -11557,13 +11621,13 @@
     </row>
     <row r="82">
       <c r="A82" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B82" s="4">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="C82" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D82" s="12">
         <v>1</v>
@@ -11588,13 +11652,13 @@
     </row>
     <row r="83">
       <c r="A83" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B83" s="4">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="C83" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D83" s="12">
         <v>1</v>
@@ -11619,13 +11683,13 @@
     </row>
     <row r="84">
       <c r="A84" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B84" s="4">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="C84" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D84" s="12">
         <v>1</v>
@@ -11650,13 +11714,13 @@
     </row>
     <row r="85">
       <c r="A85" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B85" s="4">
-        <v>16.6</v>
+        <v>16.2</v>
       </c>
       <c r="C85" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D85" s="12">
         <v>1</v>
@@ -11681,13 +11745,13 @@
     </row>
     <row r="86">
       <c r="A86" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B86" s="4">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="C86" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D86" s="12">
         <v>1</v>
@@ -11712,13 +11776,13 @@
     </row>
     <row r="87">
       <c r="A87" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B87" s="4">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="C87" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D87" s="12">
         <v>1</v>
@@ -11743,13 +11807,13 @@
     </row>
     <row r="88">
       <c r="A88" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B88" s="4">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="C88" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D88" s="12">
         <v>1</v>
@@ -11774,13 +11838,13 @@
     </row>
     <row r="89">
       <c r="A89" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B89" s="4">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="C89" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D89" s="12">
         <v>1</v>
@@ -11805,13 +11869,13 @@
     </row>
     <row r="90">
       <c r="A90" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B90" s="4">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="C90" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D90" s="12">
         <v>1</v>
@@ -11836,13 +11900,13 @@
     </row>
     <row r="91">
       <c r="A91" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B91" s="4">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="C91" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D91" s="12">
         <v>1</v>
@@ -11867,13 +11931,13 @@
     </row>
     <row r="92">
       <c r="A92" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B92" s="4">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="C92" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D92" s="12">
         <v>1</v>
@@ -11898,13 +11962,13 @@
     </row>
     <row r="93">
       <c r="A93" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B93" s="4">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="C93" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D93" s="12">
         <v>1</v>
@@ -11929,13 +11993,13 @@
     </row>
     <row r="94">
       <c r="A94" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B94" s="4">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="C94" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D94" s="12">
         <v>1</v>
@@ -11960,13 +12024,13 @@
     </row>
     <row r="95">
       <c r="A95" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B95" s="4">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="C95" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D95" s="12">
         <v>1</v>
@@ -11991,13 +12055,13 @@
     </row>
     <row r="96">
       <c r="A96" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B96" s="4">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="C96" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D96" s="12">
         <v>1</v>
@@ -12013,7 +12077,7 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="I96" s="12">
@@ -12022,13 +12086,13 @@
     </row>
     <row r="97">
       <c r="A97" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B97" s="4">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="C97" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D97" s="12">
         <v>1</v>
@@ -12053,145 +12117,145 @@
     </row>
     <row r="98">
       <c r="A98" s="9">
+        <v>820</v>
+      </c>
+      <c r="B98" s="4">
+        <v>21.1</v>
+      </c>
+      <c r="C98" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="D98" s="12">
+        <v>1</v>
+      </c>
+      <c r="E98" s="12">
+        <v>1</v>
+      </c>
+      <c r="F98" s="12">
+        <v>1</v>
+      </c>
+      <c r="G98" s="12">
+        <v>2</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="I98" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9">
         <v>840</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B99" s="4">
         <v>21.5</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C99" s="4">
         <v>29</v>
       </c>
-      <c r="D98" s="12">
-        <v>1</v>
-      </c>
-      <c r="E98" s="12">
-        <v>1</v>
-      </c>
-      <c r="F98" s="12">
-        <v>1</v>
-      </c>
-      <c r="G98" s="12">
-        <v>2</v>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
+      <c r="D99" s="12">
+        <v>1</v>
+      </c>
+      <c r="E99" s="12">
+        <v>1</v>
+      </c>
+      <c r="F99" s="12">
+        <v>1</v>
+      </c>
+      <c r="G99" s="12">
+        <v>2</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">B2s_v2 x1</t>
         </is>
       </c>
-      <c r="I98" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" ht="10" customHeight="1"/>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="I99" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Code Compass, plus 250 Code Inspector users</t>
         </is>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7"/>
-    </row>
-    <row r="101" ht="16.2" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" ht="16.2" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">All seats run Compass. 250 of them also run Code Inspector 5–7 times per working day.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Seats</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (quiet usage)</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Jobs at once (busy usage)</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Peak replicas (platform-managed)</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Warm replicas</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">vCPU per replica</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">RAM GB per replica</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Index host (size x how many)</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines to buy (index only)</t>
         </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9">
-        <v>20</v>
-      </c>
-      <c r="B103" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C103" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D103" s="12">
-        <v>1</v>
-      </c>
-      <c r="E103" s="12">
-        <v>1</v>
-      </c>
-      <c r="F103" s="12">
-        <v>1</v>
-      </c>
-      <c r="G103" s="12">
-        <v>2</v>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B2ls_v2 x1</t>
-        </is>
-      </c>
-      <c r="I103" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B104" s="4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C104" s="4">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="D104" s="12">
         <v>1</v>
@@ -12216,13 +12280,13 @@
     </row>
     <row r="105">
       <c r="A105" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B105" s="4">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="C105" s="4">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="D105" s="12">
         <v>1</v>
@@ -12247,13 +12311,13 @@
     </row>
     <row r="106">
       <c r="A106" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B106" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="C106" s="4">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="D106" s="12">
         <v>1</v>
@@ -12278,13 +12342,13 @@
     </row>
     <row r="107">
       <c r="A107" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B107" s="4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="C107" s="4">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D107" s="12">
         <v>1</v>
@@ -12309,13 +12373,13 @@
     </row>
     <row r="108">
       <c r="A108" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B108" s="4">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="C108" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D108" s="12">
         <v>1</v>
@@ -12340,13 +12404,13 @@
     </row>
     <row r="109">
       <c r="A109" s="9">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B109" s="4">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C109" s="4">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="D109" s="12">
         <v>1</v>
@@ -12371,13 +12435,13 @@
     </row>
     <row r="110">
       <c r="A110" s="9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B110" s="4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="C110" s="4">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D110" s="12">
         <v>1</v>
@@ -12402,13 +12466,13 @@
     </row>
     <row r="111">
       <c r="A111" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B111" s="4">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="C111" s="4">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="D111" s="12">
         <v>1</v>
@@ -12433,13 +12497,13 @@
     </row>
     <row r="112">
       <c r="A112" s="9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B112" s="4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="C112" s="4">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="D112" s="12">
         <v>1</v>
@@ -12464,13 +12528,13 @@
     </row>
     <row r="113">
       <c r="A113" s="9">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B113" s="4">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="C113" s="4">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="D113" s="12">
         <v>1</v>
@@ -12495,13 +12559,13 @@
     </row>
     <row r="114">
       <c r="A114" s="9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B114" s="4">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="C114" s="4">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="D114" s="12">
         <v>1</v>
@@ -12526,13 +12590,13 @@
     </row>
     <row r="115">
       <c r="A115" s="9">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B115" s="4">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="C115" s="4">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="D115" s="12">
         <v>1</v>
@@ -12557,13 +12621,13 @@
     </row>
     <row r="116">
       <c r="A116" s="9">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B116" s="4">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C116" s="4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D116" s="12">
         <v>1</v>
@@ -12588,13 +12652,13 @@
     </row>
     <row r="117">
       <c r="A117" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B117" s="4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="C117" s="4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="D117" s="12">
         <v>1</v>
@@ -12619,13 +12683,13 @@
     </row>
     <row r="118">
       <c r="A118" s="9">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B118" s="4">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="C118" s="4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D118" s="12">
         <v>1</v>
@@ -12650,13 +12714,13 @@
     </row>
     <row r="119">
       <c r="A119" s="9">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B119" s="4">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="C119" s="4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="D119" s="12">
         <v>1</v>
@@ -12681,13 +12745,13 @@
     </row>
     <row r="120">
       <c r="A120" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B120" s="4">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="C120" s="4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D120" s="12">
         <v>1</v>
@@ -12712,13 +12776,13 @@
     </row>
     <row r="121">
       <c r="A121" s="9">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B121" s="4">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="C121" s="4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D121" s="12">
         <v>1</v>
@@ -12743,13 +12807,13 @@
     </row>
     <row r="122">
       <c r="A122" s="9">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B122" s="4">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="C122" s="4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D122" s="12">
         <v>1</v>
@@ -12774,13 +12838,13 @@
     </row>
     <row r="123">
       <c r="A123" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B123" s="4">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="C123" s="4">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D123" s="12">
         <v>1</v>
@@ -12805,13 +12869,13 @@
     </row>
     <row r="124">
       <c r="A124" s="9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="B124" s="4">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="C124" s="4">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="D124" s="12">
         <v>1</v>
@@ -12836,13 +12900,13 @@
     </row>
     <row r="125">
       <c r="A125" s="9">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="B125" s="4">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="C125" s="4">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="D125" s="12">
         <v>1</v>
@@ -12867,13 +12931,13 @@
     </row>
     <row r="126">
       <c r="A126" s="9">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B126" s="4">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="C126" s="4">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D126" s="12">
         <v>1</v>
@@ -12898,13 +12962,13 @@
     </row>
     <row r="127">
       <c r="A127" s="9">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="B127" s="4">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="C127" s="4">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D127" s="12">
         <v>1</v>
@@ -12929,13 +12993,13 @@
     </row>
     <row r="128">
       <c r="A128" s="9">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B128" s="4">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="C128" s="4">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="D128" s="12">
         <v>1</v>
@@ -12960,13 +13024,13 @@
     </row>
     <row r="129">
       <c r="A129" s="9">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B129" s="4">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="C129" s="4">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D129" s="12">
         <v>1</v>
@@ -12991,13 +13055,13 @@
     </row>
     <row r="130">
       <c r="A130" s="9">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B130" s="4">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="C130" s="4">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D130" s="12">
         <v>1</v>
@@ -13022,13 +13086,13 @@
     </row>
     <row r="131">
       <c r="A131" s="9">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B131" s="4">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="C131" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D131" s="12">
         <v>1</v>
@@ -13053,13 +13117,13 @@
     </row>
     <row r="132">
       <c r="A132" s="9">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B132" s="4">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="C132" s="4">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D132" s="12">
         <v>1</v>
@@ -13084,13 +13148,13 @@
     </row>
     <row r="133">
       <c r="A133" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B133" s="4">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="C133" s="4">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="D133" s="12">
         <v>1</v>
@@ -13115,13 +13179,13 @@
     </row>
     <row r="134">
       <c r="A134" s="9">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B134" s="4">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="C134" s="4">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="D134" s="12">
         <v>1</v>
@@ -13146,13 +13210,13 @@
     </row>
     <row r="135">
       <c r="A135" s="9">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B135" s="4">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="C135" s="4">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="D135" s="12">
         <v>1</v>
@@ -13177,13 +13241,13 @@
     </row>
     <row r="136">
       <c r="A136" s="9">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B136" s="4">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="C136" s="4">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="D136" s="12">
         <v>1</v>
@@ -13208,13 +13272,13 @@
     </row>
     <row r="137">
       <c r="A137" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="B137" s="4">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="C137" s="4">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D137" s="12">
         <v>1</v>
@@ -13239,13 +13303,13 @@
     </row>
     <row r="138">
       <c r="A138" s="9">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B138" s="4">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="C138" s="4">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="D138" s="12">
         <v>1</v>
@@ -13270,13 +13334,13 @@
     </row>
     <row r="139">
       <c r="A139" s="9">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="B139" s="4">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="C139" s="4">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="D139" s="12">
         <v>1</v>
@@ -13301,13 +13365,13 @@
     </row>
     <row r="140">
       <c r="A140" s="9">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="B140" s="4">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="C140" s="4">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="D140" s="12">
         <v>1</v>
@@ -13332,13 +13396,13 @@
     </row>
     <row r="141">
       <c r="A141" s="9">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="B141" s="4">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="C141" s="4">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="D141" s="12">
         <v>1</v>
@@ -13363,13 +13427,13 @@
     </row>
     <row r="142">
       <c r="A142" s="9">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B142" s="4">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="C142" s="4">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="D142" s="12">
         <v>1</v>
@@ -13385,7 +13449,7 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2s_v2 x1</t>
+          <t xml:space="preserve">B2ls_v2 x1</t>
         </is>
       </c>
       <c r="I142" s="12">
@@ -13394,13 +13458,13 @@
     </row>
     <row r="143">
       <c r="A143" s="9">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B143" s="4">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="C143" s="4">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="D143" s="12">
         <v>1</v>
@@ -13425,47 +13489,79 @@
     </row>
     <row r="144">
       <c r="A144" s="9">
+        <v>820</v>
+      </c>
+      <c r="B144" s="4">
+        <v>22.5</v>
+      </c>
+      <c r="C144" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="D144" s="12">
+        <v>1</v>
+      </c>
+      <c r="E144" s="12">
+        <v>1</v>
+      </c>
+      <c r="F144" s="12">
+        <v>1</v>
+      </c>
+      <c r="G144" s="12">
+        <v>2</v>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B2s_v2 x1</t>
+        </is>
+      </c>
+      <c r="I144" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9">
         <v>840</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B145" s="4">
         <v>22.9</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C145" s="4">
         <v>31</v>
       </c>
-      <c r="D144" s="12">
-        <v>1</v>
-      </c>
-      <c r="E144" s="12">
-        <v>1</v>
-      </c>
-      <c r="F144" s="12">
-        <v>1</v>
-      </c>
-      <c r="G144" s="12">
-        <v>2</v>
-      </c>
-      <c r="H144" s="9" t="inlineStr">
+      <c r="D145" s="12">
+        <v>1</v>
+      </c>
+      <c r="E145" s="12">
+        <v>1</v>
+      </c>
+      <c r="F145" s="12">
+        <v>1</v>
+      </c>
+      <c r="G145" s="12">
+        <v>2</v>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">B2s_v2 x1</t>
         </is>
       </c>
-      <c r="I144" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" ht="10" customHeight="1"/>
+      <c r="I145" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" ht="10" customHeight="1"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A102:I102"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/AscendOS-Hardware-Requirements.xlsx
+++ b/AscendOS-Hardware-Requirements.xlsx
@@ -5,7 +5,8 @@
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
     <sheet name="Requirements by load" sheetId="2" r:id="rId2"/>
     <sheet name="Full detail" sheetId="3" r:id="rId3"/>
-    <sheet name="Platform requirements" sheetId="4" r:id="rId4"/>
+    <sheet name="Assumptions" sheetId="4" r:id="rId4"/>
+    <sheet name="Platform requirements" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -224,42 +225,42 @@
     <row r="12" ht="16.2" customHeight="1">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   840 people each run about 20 searches in a day    =  18,550 jobs a day</t>
+          <t xml:space="preserve">   840 seats x (20 searches + 5 estimating jobs), plus 250 x 7 scans  =  22,750 jobs a day</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the busy hour carries 3x its even share of those  =   6,956 in that hour</t>
+          <t xml:space="preserve">   the busy hour carries 3x its even share of those             =  8,531 in that hour</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   each one occupies a core for 12-55 seconds        =  most finish before the next arrives</t>
+          <t xml:space="preserve">   each one occupies a core for 12-55 seconds                   =  most finish before the next arrives</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.2" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">   so at any given instant, mid-flight               =  31 RUNNING AT ONCE</t>
+          <t xml:space="preserve">   so at any given instant, mid-flight                          =  40 RUNNING AT ONCE</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42.6" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nearly 7,000 searches an hour sounds enormous; 31 running simultaneously does not. Both are the same fact. A search takes seconds and then the core is free again, so they overlap far less than the daily total suggests. That overlap is the entire hardware question, and it is why 840 seats need about 10 vCPU rather than hundreds.</t>
+          <t xml:space="preserve">Eight and a half thousand jobs an hour sounds enormous; 40 running simultaneously does not. Both are the same fact. A job takes seconds and then the core is free again, so they overlap far less than the daily total suggests. That overlap is the entire hardware question, and it is why 840 seats need about 12 vCPU rather than hundreds.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29.4" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A number below 1 is normal too. At 20 seats it is 1.3, and for Compass alone 0.5 - meaning a job is in progress about half the busy hour and nothing is running the rest of it.</t>
+          <t xml:space="preserve">A number below 1 is normal too. At 20 seats without Code Inspector it is 0.7 - meaning a job is in progress about that share of the busy hour and nothing is running the rest of it.</t>
         </is>
       </c>
     </row>
@@ -288,56 +289,63 @@
     <row r="22" ht="42.6" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGHT CASE - every seat running Code Compass and nothing else. HEAVY CASE - the same, plus 250 people also running Code Inspector, the most demanding configuration we would expect. Any real deployment sits between the two, so they bracket the answer rather than predicting it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42.6" customHeight="1">
+          <t xml:space="preserve">WITHOUT CODE INSPECTOR - every seat running Code Compass and the estimating modules. ALL MODULES - the same, plus 250 people also running Code Inspector, the most demanding configuration we would expect. Any real deployment sits between the two, so they bracket the answer rather than predicting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55.8" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both are stated at the BUSY end of expected usage: 20 Code Compass searches per seat per working day and 7 Code Inspector scans per user. A platform sized on average usage is short on every busy day, so there is no point publishing the average. If usage settles at the quiet end (15 and 5), every figure here is about a quarter lower.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="29.4" customHeight="1">
+          <t xml:space="preserve">Both are stated at the BUSY end of expected usage: 20 Code Compass searches and 5 estimating jobs per seat per working day, plus 7 Code Inspector scans per user. A platform sized on average usage is short on every busy day, so there is no point publishing the average. If usage settles at the quiet end (15, 3 and 5), every figure here is about a quarter lower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="55.8" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">TENDER SCANS ARE EXCLUDED. They are the heaviest job the platform runs - about 95 seconds and 13 model API calls each, against 12 seconds for a Compass search - and no rate has been established for them. They are left out rather than guessed at. If tenders are going to run regularly these figures need revisiting: even one per seat per week would add roughly 5 to the "running at the same time" column at 840 seats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="29.4" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">The busiest hour is taken at 3x the flat daily average, because usage clusters at the start of the day and after lunch rather than spreading evenly.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What the figures cover, and what they do not</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42.6" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28" ht="42.6" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">The vCPU and RAM columns are the APPLICATION TIER only. The search index is listed separately because it is a fixed working set that grows with the size of the code corpus rather than with load, and because it has storage requirements the application tier does not — see the Platform requirements sheet. The two are never summed.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="29.4" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29" ht="29.4" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">These are CAPACITY figures, not availability figures. Redundancy, failover and zone spread are a separate conversation and would change the shape of any deployment built from them.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.2" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30" ht="16.2" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Not included: developer and staging environments, CI, backup targets, and pricing of any kind.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="16.2" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="16.2" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Load stages sheet: nine reference points. Full detail sheet: every 20 seats from 20 to 840, 42 rows.</t>
         </is>
@@ -404,7 +412,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGHT CASE  -  every seat running Code Compass, nothing else</t>
+          <t xml:space="preserve">WITHOUT CODE INSPECTOR  -  every seat running Code Compass and Estimating</t>
         </is>
       </c>
       <c r="B7" s="7"/>
@@ -421,7 +429,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">searches
+          <t xml:space="preserve">jobs
 per day</t>
         </is>
       </c>
@@ -455,16 +463,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C9" s="14">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D9" s="13">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F9" s="4">
         <v>1.4</v>
@@ -475,19 +483,19 @@
         <v>100</v>
       </c>
       <c r="B10" s="14">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="C10" s="14">
-        <v>750</v>
+        <v>938</v>
       </c>
       <c r="D10" s="13">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E10" s="4">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F10" s="4">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -495,19 +503,19 @@
         <v>200</v>
       </c>
       <c r="B11" s="14">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C11" s="14">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="D11" s="13">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="E11" s="4">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="F11" s="4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -515,19 +523,19 @@
         <v>300</v>
       </c>
       <c r="B12" s="14">
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="C12" s="14">
-        <v>2250</v>
+        <v>2813</v>
       </c>
       <c r="D12" s="13">
-        <v>7.5</v>
+        <v>10.6</v>
       </c>
       <c r="E12" s="4">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="F12" s="4">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="13">
@@ -535,19 +543,19 @@
         <v>400</v>
       </c>
       <c r="B13" s="14">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="C13" s="14">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="D13" s="13">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="E13" s="4">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="F13" s="4">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="14">
@@ -555,19 +563,19 @@
         <v>500</v>
       </c>
       <c r="B14" s="14">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="C14" s="14">
-        <v>3750</v>
+        <v>4688</v>
       </c>
       <c r="D14" s="13">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="E14" s="4">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="F14" s="4">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15">
@@ -575,19 +583,19 @@
         <v>600</v>
       </c>
       <c r="B15" s="14">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="C15" s="14">
-        <v>4500</v>
+        <v>5625</v>
       </c>
       <c r="D15" s="13">
-        <v>15</v>
+        <v>21.3</v>
       </c>
       <c r="E15" s="4">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="F15" s="4">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
@@ -595,19 +603,19 @@
         <v>700</v>
       </c>
       <c r="B16" s="14">
-        <v>14000</v>
+        <v>17500</v>
       </c>
       <c r="C16" s="14">
-        <v>5250</v>
+        <v>6563</v>
       </c>
       <c r="D16" s="13">
-        <v>17.5</v>
+        <v>24.8</v>
       </c>
       <c r="E16" s="4">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="F16" s="4">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="17">
@@ -615,26 +623,26 @@
         <v>840</v>
       </c>
       <c r="B17" s="14">
-        <v>16800</v>
+        <v>21000</v>
       </c>
       <c r="C17" s="14">
-        <v>6300</v>
+        <v>7875</v>
       </c>
       <c r="D17" s="13">
-        <v>21</v>
+        <v>29.8</v>
       </c>
       <c r="E17" s="4">
-        <v>6.6</v>
+        <v>9.3</v>
       </c>
       <c r="F17" s="4">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAVY CASE  -  the same, plus 250 people also running Code Inspector</t>
+          <t xml:space="preserve">ALL MODULES  -  the same, plus 250 people also running Code Inspector</t>
         </is>
       </c>
       <c r="B19" s="7"/>
@@ -685,16 +693,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="14">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="C21" s="14">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="D21" s="13">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E21" s="4">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F21" s="4">
         <v>1.7</v>
@@ -705,19 +713,19 @@
         <v>100</v>
       </c>
       <c r="B22" s="14">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="C22" s="14">
-        <v>1013</v>
+        <v>1200</v>
       </c>
       <c r="D22" s="13">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="E22" s="4">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="F22" s="4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="23">
@@ -725,19 +733,19 @@
         <v>200</v>
       </c>
       <c r="B23" s="14">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="C23" s="14">
-        <v>2025</v>
+        <v>2400</v>
       </c>
       <c r="D23" s="13">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="E23" s="4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="F23" s="4">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="24">
@@ -745,19 +753,19 @@
         <v>300</v>
       </c>
       <c r="B24" s="14">
-        <v>7750</v>
+        <v>9250</v>
       </c>
       <c r="C24" s="14">
-        <v>2906</v>
+        <v>3469</v>
       </c>
       <c r="D24" s="13">
-        <v>17.5</v>
+        <v>20.7</v>
       </c>
       <c r="E24" s="4">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="F24" s="4">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="25">
@@ -765,19 +773,19 @@
         <v>400</v>
       </c>
       <c r="B25" s="14">
-        <v>9750</v>
+        <v>11750</v>
       </c>
       <c r="C25" s="14">
-        <v>3656</v>
+        <v>4406</v>
       </c>
       <c r="D25" s="13">
-        <v>20</v>
+        <v>24.2</v>
       </c>
       <c r="E25" s="4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="F25" s="4">
-        <v>8.2</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="26">
@@ -785,19 +793,19 @@
         <v>500</v>
       </c>
       <c r="B26" s="14">
-        <v>11750</v>
+        <v>14250</v>
       </c>
       <c r="C26" s="14">
-        <v>4406</v>
+        <v>5344</v>
       </c>
       <c r="D26" s="13">
-        <v>22.5</v>
+        <v>27.7</v>
       </c>
       <c r="E26" s="4">
-        <v>7.1</v>
+        <v>8.7</v>
       </c>
       <c r="F26" s="4">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="27">
@@ -805,19 +813,19 @@
         <v>600</v>
       </c>
       <c r="B27" s="14">
-        <v>13750</v>
+        <v>16750</v>
       </c>
       <c r="C27" s="14">
-        <v>5156</v>
+        <v>6281</v>
       </c>
       <c r="D27" s="13">
-        <v>25</v>
+        <v>31.3</v>
       </c>
       <c r="E27" s="4">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="F27" s="4">
-        <v>10</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="28">
@@ -825,19 +833,19 @@
         <v>700</v>
       </c>
       <c r="B28" s="14">
-        <v>15750</v>
+        <v>19250</v>
       </c>
       <c r="C28" s="14">
-        <v>5906</v>
+        <v>7219</v>
       </c>
       <c r="D28" s="13">
-        <v>27.5</v>
+        <v>34.8</v>
       </c>
       <c r="E28" s="4">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="F28" s="4">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="29">
@@ -845,173 +853,262 @@
         <v>840</v>
       </c>
       <c r="B29" s="14">
-        <v>18550</v>
+        <v>22750</v>
       </c>
       <c r="C29" s="14">
-        <v>6956</v>
+        <v>8531</v>
       </c>
       <c r="D29" s="13">
-        <v>31</v>
+        <v>39.8</v>
       </c>
       <c r="E29" s="4">
-        <v>9.7</v>
+        <v>12.3</v>
       </c>
       <c r="F29" s="4">
-        <v>12.1</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="30" ht="10" customHeight="1"/>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEARCH INDEX  -  sized separately, never added to the above</t>
+          <t xml:space="preserve">SEARCH INDEX  -  driven by TIME, not by load</t>
         </is>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-    </row>
-    <row r="32" ht="69" customHeight="1">
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" ht="55.8" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The index does not grow with load. It grows with the size of the building-code corpus ingested, so it tracks seats only because more customers means more of their own documents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
+          <t xml:space="preserve">The index holds the ingested building codes: one book per jurisdiction, per edition. Canada has a national code plus 10 provinces and 3 territories - 14 jurisdictions - and a new National Building Code lands roughly every 4 years. Older editions are kept deliberately, because comparing across editions is a feature rather than an archive. So this figure rises on a calendar, not on a seat count, and it never falls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seats</t>
+          <t xml:space="preserve">Code editions
+kept</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Index RAM GB</t>
+          <t xml:space="preserve">Code books
+14 per edition</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Index disk GB</t>
+          <t xml:space="preserve">Building code
+GB</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer data
+GB at 840 seats</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEX RAM
+GB</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Index disk
+GB</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <v>20</v>
-      </c>
-      <c r="B34" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C34" s="12">
         <v>1</v>
+      </c>
+      <c r="B34" s="12">
+        <v>14</v>
+      </c>
+      <c r="C34" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E34" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="F34" s="12">
+        <v>12</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">today</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <v>100</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="C35" s="12">
         <v>2</v>
+      </c>
+      <c r="B35" s="12">
+        <v>28</v>
+      </c>
+      <c r="C35" s="4">
+        <v>9.3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E35" s="13">
+        <v>13.2</v>
+      </c>
+      <c r="F35" s="12">
+        <v>18</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">today</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <v>200</v>
-      </c>
-      <c r="B36" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="C36" s="12">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B36" s="12">
+        <v>42</v>
+      </c>
+      <c r="C36" s="4">
+        <v>13.9</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E36" s="4">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="12">
+        <v>24</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in about 4 years</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <v>300</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="C37" s="12">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B37" s="12">
+        <v>56</v>
+      </c>
+      <c r="C37" s="4">
+        <v>18.6</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E37" s="4">
+        <v>22.5</v>
+      </c>
+      <c r="F37" s="12">
+        <v>30</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in about 8 years</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <v>400</v>
-      </c>
-      <c r="B38" s="4">
-        <v>2.2</v>
-      </c>
-      <c r="C38" s="12">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B38" s="12">
+        <v>70</v>
+      </c>
+      <c r="C38" s="4">
+        <v>23.2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E38" s="4">
+        <v>27.1</v>
+      </c>
+      <c r="F38" s="12">
+        <v>36</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in about 12 years</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <v>500</v>
-      </c>
-      <c r="B39" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="C39" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9">
-        <v>600</v>
-      </c>
-      <c r="B40" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="C40" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9">
-        <v>700</v>
-      </c>
-      <c r="B41" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="C41" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9">
-        <v>840</v>
-      </c>
-      <c r="B42" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="C42" s="12">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" ht="10" customHeight="1"/>
-    <row r="44" ht="42.6" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="B39" s="12">
+        <v>84</v>
+      </c>
+      <c r="C39" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="E39" s="4">
+        <v>31.8</v>
+      </c>
+      <c r="F39" s="12">
+        <v>42</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in about 16 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42.6" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The customer-data column is separate: each customer organisation contributes about 5,000 vectors of their own shop knowledge and visual standards, and at 840 seats that is roughly 105 organisations. It is the smaller of the two, and unlike the code corpus it does track seats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="10" customHeight="1"/>
+    <row r="42" ht="42.6" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Between these nine points the requirement rises smoothly - there is no threshold or step change anywhere in this range. The Full detail sheet gives every 20 seats if a specific figure is needed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -1052,7 +1149,7 @@
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGHT CASE  -  Code Compass only</t>
+          <t xml:space="preserve">WITHOUT CODE INSPECTOR  -  Compass and Estimating</t>
         </is>
       </c>
       <c r="B4" s="7"/>
@@ -1069,7 +1166,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">searches
+          <t xml:space="preserve">jobs
 per day</t>
         </is>
       </c>
@@ -1103,16 +1200,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C6" s="14">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D6" s="13">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E6" s="4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F6" s="4">
         <v>1.4</v>
@@ -1123,19 +1220,19 @@
         <v>40</v>
       </c>
       <c r="B7" s="14">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="14">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D7" s="13">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E7" s="4">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F7" s="4">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -1143,19 +1240,19 @@
         <v>60</v>
       </c>
       <c r="B8" s="14">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="C8" s="14">
-        <v>450</v>
+        <v>563</v>
       </c>
       <c r="D8" s="13">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="E8" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -1163,19 +1260,19 @@
         <v>80</v>
       </c>
       <c r="B9" s="14">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="C9" s="14">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D9" s="13">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E9" s="4">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="F9" s="4">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -1183,19 +1280,19 @@
         <v>100</v>
       </c>
       <c r="B10" s="14">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="C10" s="14">
-        <v>750</v>
+        <v>938</v>
       </c>
       <c r="D10" s="13">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E10" s="4">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F10" s="4">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -1203,19 +1300,19 @@
         <v>120</v>
       </c>
       <c r="B11" s="14">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="C11" s="14">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="D11" s="13">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="E11" s="4">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F11" s="4">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -1223,19 +1320,19 @@
         <v>140</v>
       </c>
       <c r="B12" s="14">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="C12" s="14">
-        <v>1050</v>
+        <v>1313</v>
       </c>
       <c r="D12" s="13">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F12" s="4">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -1243,19 +1340,19 @@
         <v>160</v>
       </c>
       <c r="B13" s="14">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="C13" s="14">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="D13" s="13">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="E13" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -1263,19 +1360,19 @@
         <v>180</v>
       </c>
       <c r="B14" s="14">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="C14" s="14">
-        <v>1350</v>
+        <v>1688</v>
       </c>
       <c r="D14" s="13">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="E14" s="4">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F14" s="4">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1283,19 +1380,19 @@
         <v>200</v>
       </c>
       <c r="B15" s="14">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C15" s="14">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="D15" s="13">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="E15" s="4">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="F15" s="4">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16">
@@ -1303,19 +1400,19 @@
         <v>220</v>
       </c>
       <c r="B16" s="14">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="C16" s="14">
-        <v>1650</v>
+        <v>2063</v>
       </c>
       <c r="D16" s="13">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="E16" s="4">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="4">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1420,19 @@
         <v>240</v>
       </c>
       <c r="B17" s="14">
-        <v>4800</v>
+        <v>6000</v>
       </c>
       <c r="C17" s="14">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="D17" s="13">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="E17" s="4">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="F17" s="4">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18">
@@ -1343,19 +1440,19 @@
         <v>260</v>
       </c>
       <c r="B18" s="14">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="C18" s="14">
-        <v>1950</v>
+        <v>2438</v>
       </c>
       <c r="D18" s="13">
-        <v>6.5</v>
+        <v>9.2</v>
       </c>
       <c r="E18" s="4">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="F18" s="4">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="19">
@@ -1363,19 +1460,19 @@
         <v>280</v>
       </c>
       <c r="B19" s="14">
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="C19" s="14">
-        <v>2100</v>
+        <v>2625</v>
       </c>
       <c r="D19" s="13">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="E19" s="4">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="F19" s="4">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
@@ -1383,19 +1480,19 @@
         <v>300</v>
       </c>
       <c r="B20" s="14">
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="C20" s="14">
-        <v>2250</v>
+        <v>2813</v>
       </c>
       <c r="D20" s="13">
-        <v>7.5</v>
+        <v>10.6</v>
       </c>
       <c r="E20" s="4">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="4">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
@@ -1403,19 +1500,19 @@
         <v>320</v>
       </c>
       <c r="B21" s="14">
-        <v>6400</v>
+        <v>8000</v>
       </c>
       <c r="C21" s="14">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="D21" s="13">
-        <v>8</v>
+        <v>11.3</v>
       </c>
       <c r="E21" s="4">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="F21" s="4">
-        <v>4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="22">
@@ -1423,19 +1520,19 @@
         <v>340</v>
       </c>
       <c r="B22" s="14">
-        <v>6800</v>
+        <v>8500</v>
       </c>
       <c r="C22" s="14">
-        <v>2550</v>
+        <v>3188</v>
       </c>
       <c r="D22" s="13">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="E22" s="4">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="F22" s="4">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="23">
@@ -1443,19 +1540,19 @@
         <v>360</v>
       </c>
       <c r="B23" s="14">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="C23" s="14">
-        <v>2700</v>
+        <v>3375</v>
       </c>
       <c r="D23" s="13">
-        <v>9</v>
+        <v>12.8</v>
       </c>
       <c r="E23" s="4">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="F23" s="4">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="24">
@@ -1463,19 +1560,19 @@
         <v>380</v>
       </c>
       <c r="B24" s="14">
-        <v>7600</v>
+        <v>9500</v>
       </c>
       <c r="C24" s="14">
-        <v>2850</v>
+        <v>3563</v>
       </c>
       <c r="D24" s="13">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="E24" s="4">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="F24" s="4">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="25">
@@ -1483,19 +1580,19 @@
         <v>400</v>
       </c>
       <c r="B25" s="14">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="C25" s="14">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="D25" s="13">
-        <v>10</v>
+        <v>14.2</v>
       </c>
       <c r="E25" s="4">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="F25" s="4">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="26">
@@ -1503,19 +1600,19 @@
         <v>420</v>
       </c>
       <c r="B26" s="14">
-        <v>8400</v>
+        <v>10500</v>
       </c>
       <c r="C26" s="14">
-        <v>3150</v>
+        <v>3938</v>
       </c>
       <c r="D26" s="13">
-        <v>10.5</v>
+        <v>14.9</v>
       </c>
       <c r="E26" s="4">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="F26" s="4">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
@@ -1523,19 +1620,19 @@
         <v>440</v>
       </c>
       <c r="B27" s="14">
-        <v>8800</v>
+        <v>11000</v>
       </c>
       <c r="C27" s="14">
-        <v>3300</v>
+        <v>4125</v>
       </c>
       <c r="D27" s="13">
-        <v>11</v>
+        <v>15.6</v>
       </c>
       <c r="E27" s="4">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="4">
-        <v>5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="28">
@@ -1543,19 +1640,19 @@
         <v>460</v>
       </c>
       <c r="B28" s="14">
-        <v>9200</v>
+        <v>11500</v>
       </c>
       <c r="C28" s="14">
-        <v>3450</v>
+        <v>4313</v>
       </c>
       <c r="D28" s="13">
-        <v>11.5</v>
+        <v>16.3</v>
       </c>
       <c r="E28" s="4">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="F28" s="4">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="29">
@@ -1563,19 +1660,19 @@
         <v>480</v>
       </c>
       <c r="B29" s="14">
-        <v>9600</v>
+        <v>12000</v>
       </c>
       <c r="C29" s="14">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="D29" s="13">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E29" s="4">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="F29" s="4">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30">
@@ -1583,19 +1680,19 @@
         <v>500</v>
       </c>
       <c r="B30" s="14">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="C30" s="14">
-        <v>3750</v>
+        <v>4688</v>
       </c>
       <c r="D30" s="13">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="E30" s="4">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="F30" s="4">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="31">
@@ -1603,19 +1700,19 @@
         <v>520</v>
       </c>
       <c r="B31" s="14">
-        <v>10400</v>
+        <v>13000</v>
       </c>
       <c r="C31" s="14">
-        <v>3900</v>
+        <v>4875</v>
       </c>
       <c r="D31" s="13">
-        <v>13</v>
+        <v>18.4</v>
       </c>
       <c r="E31" s="4">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="F31" s="4">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="32">
@@ -1623,19 +1720,19 @@
         <v>540</v>
       </c>
       <c r="B32" s="14">
-        <v>10800</v>
+        <v>13500</v>
       </c>
       <c r="C32" s="14">
-        <v>4050</v>
+        <v>5063</v>
       </c>
       <c r="D32" s="13">
-        <v>13.5</v>
+        <v>19.1</v>
       </c>
       <c r="E32" s="4">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="F32" s="4">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="33">
@@ -1643,19 +1740,19 @@
         <v>560</v>
       </c>
       <c r="B33" s="14">
-        <v>11200</v>
+        <v>14000</v>
       </c>
       <c r="C33" s="14">
-        <v>4200</v>
+        <v>5250</v>
       </c>
       <c r="D33" s="13">
-        <v>14</v>
+        <v>19.8</v>
       </c>
       <c r="E33" s="4">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="F33" s="4">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="34">
@@ -1663,19 +1760,19 @@
         <v>580</v>
       </c>
       <c r="B34" s="14">
-        <v>11600</v>
+        <v>14500</v>
       </c>
       <c r="C34" s="14">
-        <v>4350</v>
+        <v>5438</v>
       </c>
       <c r="D34" s="13">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="E34" s="4">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="F34" s="4">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="35">
@@ -1683,19 +1780,19 @@
         <v>600</v>
       </c>
       <c r="B35" s="14">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="C35" s="14">
-        <v>4500</v>
+        <v>5625</v>
       </c>
       <c r="D35" s="13">
-        <v>15</v>
+        <v>21.3</v>
       </c>
       <c r="E35" s="4">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="F35" s="4">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="36">
@@ -1703,19 +1800,19 @@
         <v>620</v>
       </c>
       <c r="B36" s="14">
-        <v>12400</v>
+        <v>15500</v>
       </c>
       <c r="C36" s="14">
-        <v>4650</v>
+        <v>5813</v>
       </c>
       <c r="D36" s="13">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="E36" s="4">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="F36" s="4">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1723,19 +1820,19 @@
         <v>640</v>
       </c>
       <c r="B37" s="14">
-        <v>12800</v>
+        <v>16000</v>
       </c>
       <c r="C37" s="14">
-        <v>4800</v>
+        <v>6000</v>
       </c>
       <c r="D37" s="13">
-        <v>16</v>
+        <v>22.7</v>
       </c>
       <c r="E37" s="4">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="F37" s="4">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="38">
@@ -1743,19 +1840,19 @@
         <v>660</v>
       </c>
       <c r="B38" s="14">
-        <v>13200</v>
+        <v>16500</v>
       </c>
       <c r="C38" s="14">
-        <v>4950</v>
+        <v>6188</v>
       </c>
       <c r="D38" s="13">
-        <v>16.5</v>
+        <v>23.4</v>
       </c>
       <c r="E38" s="4">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="F38" s="4">
-        <v>7</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="39">
@@ -1763,19 +1860,19 @@
         <v>680</v>
       </c>
       <c r="B39" s="14">
-        <v>13600</v>
+        <v>17000</v>
       </c>
       <c r="C39" s="14">
-        <v>5100</v>
+        <v>6375</v>
       </c>
       <c r="D39" s="13">
-        <v>17</v>
+        <v>24.1</v>
       </c>
       <c r="E39" s="4">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="F39" s="4">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="40">
@@ -1783,19 +1880,19 @@
         <v>700</v>
       </c>
       <c r="B40" s="14">
-        <v>14000</v>
+        <v>17500</v>
       </c>
       <c r="C40" s="14">
-        <v>5250</v>
+        <v>6563</v>
       </c>
       <c r="D40" s="13">
-        <v>17.5</v>
+        <v>24.8</v>
       </c>
       <c r="E40" s="4">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="F40" s="4">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="41">
@@ -1803,19 +1900,19 @@
         <v>720</v>
       </c>
       <c r="B41" s="14">
-        <v>14400</v>
+        <v>18000</v>
       </c>
       <c r="C41" s="14">
-        <v>5400</v>
+        <v>6750</v>
       </c>
       <c r="D41" s="13">
-        <v>18</v>
+        <v>25.5</v>
       </c>
       <c r="E41" s="4">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="42">
@@ -1823,19 +1920,19 @@
         <v>740</v>
       </c>
       <c r="B42" s="14">
-        <v>14800</v>
+        <v>18500</v>
       </c>
       <c r="C42" s="14">
-        <v>5550</v>
+        <v>6938</v>
       </c>
       <c r="D42" s="13">
-        <v>18.5</v>
+        <v>26.2</v>
       </c>
       <c r="E42" s="4">
-        <v>5.9</v>
+        <v>8.2</v>
       </c>
       <c r="F42" s="4">
-        <v>7.7</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="43">
@@ -1843,19 +1940,19 @@
         <v>760</v>
       </c>
       <c r="B43" s="14">
-        <v>15200</v>
+        <v>19000</v>
       </c>
       <c r="C43" s="14">
-        <v>5700</v>
+        <v>7125</v>
       </c>
       <c r="D43" s="13">
-        <v>19</v>
+        <v>26.9</v>
       </c>
       <c r="E43" s="4">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="F43" s="4">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="44">
@@ -1863,19 +1960,19 @@
         <v>780</v>
       </c>
       <c r="B44" s="14">
-        <v>15600</v>
+        <v>19500</v>
       </c>
       <c r="C44" s="14">
-        <v>5850</v>
+        <v>7313</v>
       </c>
       <c r="D44" s="13">
-        <v>19.5</v>
+        <v>27.6</v>
       </c>
       <c r="E44" s="4">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="F44" s="4">
-        <v>8</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="45">
@@ -1883,19 +1980,19 @@
         <v>800</v>
       </c>
       <c r="B45" s="14">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="C45" s="14">
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="D45" s="13">
-        <v>20</v>
+        <v>28.3</v>
       </c>
       <c r="E45" s="4">
-        <v>6.3</v>
+        <v>8.8</v>
       </c>
       <c r="F45" s="4">
-        <v>8.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="46">
@@ -1903,19 +2000,19 @@
         <v>820</v>
       </c>
       <c r="B46" s="14">
-        <v>16400</v>
+        <v>20500</v>
       </c>
       <c r="C46" s="14">
-        <v>6150</v>
+        <v>7688</v>
       </c>
       <c r="D46" s="13">
-        <v>20.5</v>
+        <v>29</v>
       </c>
       <c r="E46" s="4">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="F46" s="4">
-        <v>8.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="47">
@@ -1923,26 +2020,26 @@
         <v>840</v>
       </c>
       <c r="B47" s="14">
-        <v>16800</v>
+        <v>21000</v>
       </c>
       <c r="C47" s="14">
-        <v>6300</v>
+        <v>7875</v>
       </c>
       <c r="D47" s="13">
-        <v>21</v>
+        <v>29.8</v>
       </c>
       <c r="E47" s="4">
-        <v>6.6</v>
+        <v>9.3</v>
       </c>
       <c r="F47" s="4">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="48" ht="10" customHeight="1"/>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEAVY CASE  -  plus 250 Code Inspector users</t>
+          <t xml:space="preserve">ALL MODULES  -  plus 250 Code Inspector users</t>
         </is>
       </c>
       <c r="B49" s="7"/>
@@ -1993,16 +2090,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="14">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="C51" s="14">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="D51" s="13">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E51" s="4">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F51" s="4">
         <v>1.7</v>
@@ -2013,19 +2110,19 @@
         <v>40</v>
       </c>
       <c r="B52" s="14">
-        <v>1080</v>
+        <v>1280</v>
       </c>
       <c r="C52" s="14">
-        <v>405</v>
+        <v>480</v>
       </c>
       <c r="D52" s="13">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E52" s="4">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F52" s="4">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="53">
@@ -2033,19 +2130,19 @@
         <v>60</v>
       </c>
       <c r="B53" s="14">
-        <v>1620</v>
+        <v>1920</v>
       </c>
       <c r="C53" s="14">
-        <v>608</v>
+        <v>720</v>
       </c>
       <c r="D53" s="13">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="E53" s="4">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F53" s="4">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="54">
@@ -2053,19 +2150,19 @@
         <v>80</v>
       </c>
       <c r="B54" s="14">
-        <v>2160</v>
+        <v>2560</v>
       </c>
       <c r="C54" s="14">
-        <v>810</v>
+        <v>960</v>
       </c>
       <c r="D54" s="13">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E54" s="4">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="F54" s="4">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="55">
@@ -2073,19 +2170,19 @@
         <v>100</v>
       </c>
       <c r="B55" s="14">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="C55" s="14">
-        <v>1013</v>
+        <v>1200</v>
       </c>
       <c r="D55" s="13">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="E55" s="4">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="F55" s="4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="56">
@@ -2093,19 +2190,19 @@
         <v>120</v>
       </c>
       <c r="B56" s="14">
-        <v>3240</v>
+        <v>3840</v>
       </c>
       <c r="C56" s="14">
-        <v>1215</v>
+        <v>1440</v>
       </c>
       <c r="D56" s="13">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="E56" s="4">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="F56" s="4">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="57">
@@ -2113,19 +2210,19 @@
         <v>140</v>
       </c>
       <c r="B57" s="14">
-        <v>3780</v>
+        <v>4480</v>
       </c>
       <c r="C57" s="14">
-        <v>1418</v>
+        <v>1680</v>
       </c>
       <c r="D57" s="13">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="E57" s="4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="F57" s="4">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="58">
@@ -2133,19 +2230,19 @@
         <v>160</v>
       </c>
       <c r="B58" s="14">
-        <v>4320</v>
+        <v>5120</v>
       </c>
       <c r="C58" s="14">
-        <v>1620</v>
+        <v>1920</v>
       </c>
       <c r="D58" s="13">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="E58" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="4">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="59">
@@ -2153,19 +2250,19 @@
         <v>180</v>
       </c>
       <c r="B59" s="14">
-        <v>4860</v>
+        <v>5760</v>
       </c>
       <c r="C59" s="14">
-        <v>1823</v>
+        <v>2160</v>
       </c>
       <c r="D59" s="13">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="E59" s="4">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="F59" s="4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -2173,19 +2270,19 @@
         <v>200</v>
       </c>
       <c r="B60" s="14">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="C60" s="14">
-        <v>2025</v>
+        <v>2400</v>
       </c>
       <c r="D60" s="13">
-        <v>13</v>
+        <v>15.1</v>
       </c>
       <c r="E60" s="4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="F60" s="4">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="61">
@@ -2193,19 +2290,19 @@
         <v>220</v>
       </c>
       <c r="B61" s="14">
-        <v>5940</v>
+        <v>7040</v>
       </c>
       <c r="C61" s="14">
-        <v>2228</v>
+        <v>2640</v>
       </c>
       <c r="D61" s="13">
-        <v>14.3</v>
+        <v>16.6</v>
       </c>
       <c r="E61" s="4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="F61" s="4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -2213,19 +2310,19 @@
         <v>240</v>
       </c>
       <c r="B62" s="14">
-        <v>6480</v>
+        <v>7680</v>
       </c>
       <c r="C62" s="14">
-        <v>2430</v>
+        <v>2880</v>
       </c>
       <c r="D62" s="13">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="E62" s="4">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="F62" s="4">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="63">
@@ -2233,19 +2330,19 @@
         <v>260</v>
       </c>
       <c r="B63" s="14">
-        <v>6950</v>
+        <v>8250</v>
       </c>
       <c r="C63" s="14">
-        <v>2606</v>
+        <v>3094</v>
       </c>
       <c r="D63" s="13">
-        <v>16.5</v>
+        <v>19.2</v>
       </c>
       <c r="E63" s="4">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="F63" s="4">
-        <v>7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="64">
@@ -2253,19 +2350,19 @@
         <v>280</v>
       </c>
       <c r="B64" s="14">
-        <v>7350</v>
+        <v>8750</v>
       </c>
       <c r="C64" s="14">
-        <v>2756</v>
+        <v>3281</v>
       </c>
       <c r="D64" s="13">
-        <v>17</v>
+        <v>19.9</v>
       </c>
       <c r="E64" s="4">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="F64" s="4">
-        <v>7.2</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="65">
@@ -2273,19 +2370,19 @@
         <v>300</v>
       </c>
       <c r="B65" s="14">
-        <v>7750</v>
+        <v>9250</v>
       </c>
       <c r="C65" s="14">
-        <v>2906</v>
+        <v>3469</v>
       </c>
       <c r="D65" s="13">
-        <v>17.5</v>
+        <v>20.7</v>
       </c>
       <c r="E65" s="4">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="F65" s="4">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="66">
@@ -2293,19 +2390,19 @@
         <v>320</v>
       </c>
       <c r="B66" s="14">
-        <v>8150</v>
+        <v>9750</v>
       </c>
       <c r="C66" s="14">
-        <v>3056</v>
+        <v>3656</v>
       </c>
       <c r="D66" s="13">
-        <v>18</v>
+        <v>21.4</v>
       </c>
       <c r="E66" s="4">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="F66" s="4">
-        <v>7.5</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="67">
@@ -2313,19 +2410,19 @@
         <v>340</v>
       </c>
       <c r="B67" s="14">
-        <v>8550</v>
+        <v>10250</v>
       </c>
       <c r="C67" s="14">
-        <v>3206</v>
+        <v>3844</v>
       </c>
       <c r="D67" s="13">
-        <v>18.5</v>
+        <v>22.1</v>
       </c>
       <c r="E67" s="4">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="68">
@@ -2333,19 +2430,19 @@
         <v>360</v>
       </c>
       <c r="B68" s="14">
-        <v>8950</v>
+        <v>10750</v>
       </c>
       <c r="C68" s="14">
-        <v>3356</v>
+        <v>4031</v>
       </c>
       <c r="D68" s="13">
-        <v>19</v>
+        <v>22.8</v>
       </c>
       <c r="E68" s="4">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="F68" s="4">
-        <v>7.9</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="69">
@@ -2353,19 +2450,19 @@
         <v>380</v>
       </c>
       <c r="B69" s="14">
-        <v>9350</v>
+        <v>11250</v>
       </c>
       <c r="C69" s="14">
-        <v>3506</v>
+        <v>4219</v>
       </c>
       <c r="D69" s="13">
-        <v>19.5</v>
+        <v>23.5</v>
       </c>
       <c r="E69" s="4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="F69" s="4">
-        <v>8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="70">
@@ -2373,19 +2470,19 @@
         <v>400</v>
       </c>
       <c r="B70" s="14">
-        <v>9750</v>
+        <v>11750</v>
       </c>
       <c r="C70" s="14">
-        <v>3656</v>
+        <v>4406</v>
       </c>
       <c r="D70" s="13">
-        <v>20</v>
+        <v>24.2</v>
       </c>
       <c r="E70" s="4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="F70" s="4">
-        <v>8.2</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="71">
@@ -2393,19 +2490,19 @@
         <v>420</v>
       </c>
       <c r="B71" s="14">
-        <v>10150</v>
+        <v>12250</v>
       </c>
       <c r="C71" s="14">
-        <v>3806</v>
+        <v>4594</v>
       </c>
       <c r="D71" s="13">
-        <v>20.5</v>
+        <v>24.9</v>
       </c>
       <c r="E71" s="4">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="F71" s="4">
-        <v>8.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="72">
@@ -2413,19 +2510,19 @@
         <v>440</v>
       </c>
       <c r="B72" s="14">
-        <v>10550</v>
+        <v>12750</v>
       </c>
       <c r="C72" s="14">
-        <v>3956</v>
+        <v>4781</v>
       </c>
       <c r="D72" s="13">
-        <v>21</v>
+        <v>25.6</v>
       </c>
       <c r="E72" s="4">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="F72" s="4">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="73">
@@ -2433,19 +2530,19 @@
         <v>460</v>
       </c>
       <c r="B73" s="14">
-        <v>10950</v>
+        <v>13250</v>
       </c>
       <c r="C73" s="14">
-        <v>4106</v>
+        <v>4969</v>
       </c>
       <c r="D73" s="13">
-        <v>21.5</v>
+        <v>26.3</v>
       </c>
       <c r="E73" s="4">
-        <v>6.8</v>
+        <v>8.2</v>
       </c>
       <c r="F73" s="4">
-        <v>8.7</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="74">
@@ -2453,19 +2550,19 @@
         <v>480</v>
       </c>
       <c r="B74" s="14">
-        <v>11350</v>
+        <v>13750</v>
       </c>
       <c r="C74" s="14">
-        <v>4256</v>
+        <v>5156</v>
       </c>
       <c r="D74" s="13">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E74" s="4">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F74" s="4">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="75">
@@ -2473,19 +2570,19 @@
         <v>500</v>
       </c>
       <c r="B75" s="14">
-        <v>11750</v>
+        <v>14250</v>
       </c>
       <c r="C75" s="14">
-        <v>4406</v>
+        <v>5344</v>
       </c>
       <c r="D75" s="13">
-        <v>22.5</v>
+        <v>27.7</v>
       </c>
       <c r="E75" s="4">
-        <v>7.1</v>
+        <v>8.7</v>
       </c>
       <c r="F75" s="4">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="76">
@@ -2493,19 +2590,19 @@
         <v>520</v>
       </c>
       <c r="B76" s="14">
-        <v>12150</v>
+        <v>14750</v>
       </c>
       <c r="C76" s="14">
-        <v>4556</v>
+        <v>5531</v>
       </c>
       <c r="D76" s="13">
-        <v>23</v>
+        <v>28.4</v>
       </c>
       <c r="E76" s="4">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="F76" s="4">
-        <v>9.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="77">
@@ -2513,19 +2610,19 @@
         <v>540</v>
       </c>
       <c r="B77" s="14">
-        <v>12550</v>
+        <v>15250</v>
       </c>
       <c r="C77" s="14">
-        <v>4706</v>
+        <v>5719</v>
       </c>
       <c r="D77" s="13">
-        <v>23.5</v>
+        <v>29.2</v>
       </c>
       <c r="E77" s="4">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="F77" s="4">
-        <v>9.4</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="78">
@@ -2533,19 +2630,19 @@
         <v>560</v>
       </c>
       <c r="B78" s="14">
-        <v>12950</v>
+        <v>15750</v>
       </c>
       <c r="C78" s="14">
-        <v>4856</v>
+        <v>5906</v>
       </c>
       <c r="D78" s="13">
-        <v>24</v>
+        <v>29.9</v>
       </c>
       <c r="E78" s="4">
-        <v>7.6</v>
+        <v>9.3</v>
       </c>
       <c r="F78" s="4">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="79">
@@ -2553,19 +2650,19 @@
         <v>580</v>
       </c>
       <c r="B79" s="14">
-        <v>13350</v>
+        <v>16250</v>
       </c>
       <c r="C79" s="14">
-        <v>5006</v>
+        <v>6094</v>
       </c>
       <c r="D79" s="13">
-        <v>24.5</v>
+        <v>30.6</v>
       </c>
       <c r="E79" s="4">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="F79" s="4">
-        <v>9.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="80">
@@ -2573,19 +2670,19 @@
         <v>600</v>
       </c>
       <c r="B80" s="14">
-        <v>13750</v>
+        <v>16750</v>
       </c>
       <c r="C80" s="14">
-        <v>5156</v>
+        <v>6281</v>
       </c>
       <c r="D80" s="13">
-        <v>25</v>
+        <v>31.3</v>
       </c>
       <c r="E80" s="4">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="F80" s="4">
-        <v>10</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="81">
@@ -2593,19 +2690,19 @@
         <v>620</v>
       </c>
       <c r="B81" s="14">
-        <v>14150</v>
+        <v>17250</v>
       </c>
       <c r="C81" s="14">
-        <v>5306</v>
+        <v>6469</v>
       </c>
       <c r="D81" s="13">
-        <v>25.5</v>
+        <v>32</v>
       </c>
       <c r="E81" s="4">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="F81" s="4">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="82">
@@ -2613,19 +2710,19 @@
         <v>640</v>
       </c>
       <c r="B82" s="14">
-        <v>14550</v>
+        <v>17750</v>
       </c>
       <c r="C82" s="14">
-        <v>5456</v>
+        <v>6656</v>
       </c>
       <c r="D82" s="13">
-        <v>26</v>
+        <v>32.7</v>
       </c>
       <c r="E82" s="4">
-        <v>8.2</v>
+        <v>10.2</v>
       </c>
       <c r="F82" s="4">
-        <v>10.3</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="83">
@@ -2633,19 +2730,19 @@
         <v>660</v>
       </c>
       <c r="B83" s="14">
-        <v>14950</v>
+        <v>18250</v>
       </c>
       <c r="C83" s="14">
-        <v>5606</v>
+        <v>6844</v>
       </c>
       <c r="D83" s="13">
-        <v>26.5</v>
+        <v>33.4</v>
       </c>
       <c r="E83" s="4">
-        <v>8.3</v>
+        <v>10.4</v>
       </c>
       <c r="F83" s="4">
-        <v>10.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="84">
@@ -2653,19 +2750,19 @@
         <v>680</v>
       </c>
       <c r="B84" s="14">
-        <v>15350</v>
+        <v>18750</v>
       </c>
       <c r="C84" s="14">
-        <v>5756</v>
+        <v>7031</v>
       </c>
       <c r="D84" s="13">
-        <v>27</v>
+        <v>34.1</v>
       </c>
       <c r="E84" s="4">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="F84" s="4">
-        <v>10.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="85">
@@ -2673,19 +2770,19 @@
         <v>700</v>
       </c>
       <c r="B85" s="14">
-        <v>15750</v>
+        <v>19250</v>
       </c>
       <c r="C85" s="14">
-        <v>5906</v>
+        <v>7219</v>
       </c>
       <c r="D85" s="13">
-        <v>27.5</v>
+        <v>34.8</v>
       </c>
       <c r="E85" s="4">
-        <v>8.6</v>
+        <v>10.8</v>
       </c>
       <c r="F85" s="4">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="86">
@@ -2693,19 +2790,19 @@
         <v>720</v>
       </c>
       <c r="B86" s="14">
-        <v>16150</v>
+        <v>19750</v>
       </c>
       <c r="C86" s="14">
-        <v>6056</v>
+        <v>7406</v>
       </c>
       <c r="D86" s="13">
-        <v>28</v>
+        <v>35.5</v>
       </c>
       <c r="E86" s="4">
-        <v>8.8</v>
+        <v>11</v>
       </c>
       <c r="F86" s="4">
-        <v>11</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="87">
@@ -2713,19 +2810,19 @@
         <v>740</v>
       </c>
       <c r="B87" s="14">
-        <v>16550</v>
+        <v>20250</v>
       </c>
       <c r="C87" s="14">
-        <v>6206</v>
+        <v>7594</v>
       </c>
       <c r="D87" s="13">
-        <v>28.5</v>
+        <v>36.2</v>
       </c>
       <c r="E87" s="4">
-        <v>8.9</v>
+        <v>11.2</v>
       </c>
       <c r="F87" s="4">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="88">
@@ -2733,19 +2830,19 @@
         <v>760</v>
       </c>
       <c r="B88" s="14">
-        <v>16950</v>
+        <v>20750</v>
       </c>
       <c r="C88" s="14">
-        <v>6356</v>
+        <v>7781</v>
       </c>
       <c r="D88" s="13">
-        <v>29</v>
+        <v>36.9</v>
       </c>
       <c r="E88" s="4">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
       <c r="F88" s="4">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="89">
@@ -2753,19 +2850,19 @@
         <v>780</v>
       </c>
       <c r="B89" s="14">
-        <v>17350</v>
+        <v>21250</v>
       </c>
       <c r="C89" s="14">
-        <v>6506</v>
+        <v>7969</v>
       </c>
       <c r="D89" s="13">
-        <v>29.5</v>
+        <v>37.7</v>
       </c>
       <c r="E89" s="4">
-        <v>9.2</v>
+        <v>11.6</v>
       </c>
       <c r="F89" s="4">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="90">
@@ -2773,19 +2870,19 @@
         <v>800</v>
       </c>
       <c r="B90" s="14">
-        <v>17750</v>
+        <v>21750</v>
       </c>
       <c r="C90" s="14">
-        <v>6656</v>
+        <v>8156</v>
       </c>
       <c r="D90" s="13">
-        <v>30</v>
+        <v>38.4</v>
       </c>
       <c r="E90" s="4">
-        <v>9.4</v>
+        <v>11.9</v>
       </c>
       <c r="F90" s="4">
-        <v>11.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="91">
@@ -2793,19 +2890,19 @@
         <v>820</v>
       </c>
       <c r="B91" s="14">
-        <v>18150</v>
+        <v>22250</v>
       </c>
       <c r="C91" s="14">
-        <v>6806</v>
+        <v>8344</v>
       </c>
       <c r="D91" s="13">
-        <v>30.5</v>
+        <v>39.1</v>
       </c>
       <c r="E91" s="4">
-        <v>9.5</v>
+        <v>12.1</v>
       </c>
       <c r="F91" s="4">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="92">
@@ -2813,516 +2910,27 @@
         <v>840</v>
       </c>
       <c r="B92" s="14">
-        <v>18550</v>
+        <v>22750</v>
       </c>
       <c r="C92" s="14">
-        <v>6956</v>
+        <v>8531</v>
       </c>
       <c r="D92" s="13">
-        <v>31</v>
+        <v>39.8</v>
       </c>
       <c r="E92" s="4">
-        <v>9.7</v>
+        <v>12.3</v>
       </c>
       <c r="F92" s="4">
-        <v>12.1</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="93" ht="10" customHeight="1"/>
-    <row r="94" ht="19" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEARCH INDEX</t>
-        </is>
-      </c>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seats</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Index RAM GB</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Index disk GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9">
-        <v>20</v>
-      </c>
-      <c r="B96" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C96" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9">
-        <v>40</v>
-      </c>
-      <c r="B97" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="C97" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="9">
-        <v>60</v>
-      </c>
-      <c r="B98" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="C98" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9">
-        <v>80</v>
-      </c>
-      <c r="B99" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="C99" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9">
-        <v>100</v>
-      </c>
-      <c r="B100" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="C100" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9">
-        <v>120</v>
-      </c>
-      <c r="B101" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="C101" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9">
-        <v>140</v>
-      </c>
-      <c r="B102" s="4">
-        <v>1</v>
-      </c>
-      <c r="C102" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9">
-        <v>160</v>
-      </c>
-      <c r="B103" s="4">
-        <v>1.1</v>
-      </c>
-      <c r="C103" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9">
-        <v>180</v>
-      </c>
-      <c r="B104" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="C104" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9">
-        <v>200</v>
-      </c>
-      <c r="B105" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="C105" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="9">
-        <v>220</v>
-      </c>
-      <c r="B106" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="C106" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="9">
-        <v>240</v>
-      </c>
-      <c r="B107" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="C107" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="9">
-        <v>260</v>
-      </c>
-      <c r="B108" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="C108" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9">
-        <v>280</v>
-      </c>
-      <c r="B109" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="C109" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9">
-        <v>300</v>
-      </c>
-      <c r="B110" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="C110" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9">
-        <v>320</v>
-      </c>
-      <c r="B111" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="C111" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9">
-        <v>340</v>
-      </c>
-      <c r="B112" s="4">
-        <v>1.9</v>
-      </c>
-      <c r="C112" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9">
-        <v>360</v>
-      </c>
-      <c r="B113" s="4">
-        <v>2</v>
-      </c>
-      <c r="C113" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9">
-        <v>380</v>
-      </c>
-      <c r="B114" s="4">
-        <v>2.1</v>
-      </c>
-      <c r="C114" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9">
-        <v>400</v>
-      </c>
-      <c r="B115" s="4">
-        <v>2.2</v>
-      </c>
-      <c r="C115" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9">
-        <v>420</v>
-      </c>
-      <c r="B116" s="4">
-        <v>2.3</v>
-      </c>
-      <c r="C116" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9">
-        <v>440</v>
-      </c>
-      <c r="B117" s="4">
-        <v>2.4</v>
-      </c>
-      <c r="C117" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9">
-        <v>460</v>
-      </c>
-      <c r="B118" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="C118" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9">
-        <v>480</v>
-      </c>
-      <c r="B119" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="C119" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9">
-        <v>500</v>
-      </c>
-      <c r="B120" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="C120" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9">
-        <v>520</v>
-      </c>
-      <c r="B121" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="C121" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9">
-        <v>540</v>
-      </c>
-      <c r="B122" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="C122" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9">
-        <v>560</v>
-      </c>
-      <c r="B123" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="C123" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9">
-        <v>580</v>
-      </c>
-      <c r="B124" s="4">
-        <v>3</v>
-      </c>
-      <c r="C124" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9">
-        <v>600</v>
-      </c>
-      <c r="B125" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="C125" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9">
-        <v>620</v>
-      </c>
-      <c r="B126" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="C126" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9">
-        <v>640</v>
-      </c>
-      <c r="B127" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="C127" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9">
-        <v>660</v>
-      </c>
-      <c r="B128" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="C128" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9">
-        <v>680</v>
-      </c>
-      <c r="B129" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="C129" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9">
-        <v>700</v>
-      </c>
-      <c r="B130" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="C130" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="9">
-        <v>720</v>
-      </c>
-      <c r="B131" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="C131" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="9">
-        <v>740</v>
-      </c>
-      <c r="B132" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="C132" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9">
-        <v>760</v>
-      </c>
-      <c r="B133" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="C133" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="9">
-        <v>780</v>
-      </c>
-      <c r="B134" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="C134" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9">
-        <v>800</v>
-      </c>
-      <c r="B135" s="4">
-        <v>4</v>
-      </c>
-      <c r="C135" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9">
-        <v>820</v>
-      </c>
-      <c r="B136" s="4">
-        <v>4.1</v>
-      </c>
-      <c r="C136" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9">
-        <v>840</v>
-      </c>
-      <c r="B137" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="C137" s="12">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A94:C94"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
@@ -3337,6 +2945,415 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.2" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every input these figures depend on, and where each one came from. If any of it is wrong the numbers move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Compass searches</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15–20 per seat per working day</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stated by Ironwood</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimating jobs</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3–5 per seat per working day</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stated by Ironwood</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Inspector scans</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5–7 per user per working day, for the named subset</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stated by Ironwood</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tender scans</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXCLUDED — no rate established</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaviest job on the platform. See note below</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compass job duration</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 seconds, 3 model API calls</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured in the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimating job duration</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 seconds, 3 model API calls</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured in the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector job duration</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55 seconds, 4 model API calls</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured in the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tender job duration</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95 seconds, 13 model API calls</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured in the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Working day</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 hours</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Busiest hour</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3× the flat daily average</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assumption — usage clusters morning and after lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seats per customer organisation</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assumption — McLean’s runs 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jurisdictions in the corpus</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 — 1 national + 10 provinces + 3 territories</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canadian building code coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code editions retained</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 today, +1 every 4 years</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Older editions kept for comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vectors per code book</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45,000</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured from an ingested book</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vectors per customer org</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5,000</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop knowledge, visual SOPs, vision training</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bytes per vector</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5,272 — 768 dimensions float32 plus payload text</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Index memory overhead</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4×</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HNSW graph and payload indexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU per concurrent job</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.30 vCPU, plus 0.35 baseline</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derived from platform measurements</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Memory per concurrent job</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.35 GB, plus 1.20 GB baseline</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derived from platform measurements</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The one open item</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42.6" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tender scans are excluded because no usage rate has been established for them, and they are by some distance the heaviest job the platform runs - roughly 95 seconds and 13 model API calls each. Everything else above is either measured or stated. If tender scanning is going to be part of normal use, these figures need redoing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derived, not assumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42.6" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The vCPU and memory figures come from the two coefficients at the bottom of the table applied to the concurrency figure, which itself comes from the usage rates and job durations above it. Nothing in the requirement columns is a judgement laid on top - change an input and the whole chain moves with it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
   </cols>
   <sheetData>

--- a/AscendOS-Hardware-Requirements.xlsx
+++ b/AscendOS-Hardware-Requirements.xlsx
@@ -186,124 +186,124 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="55.8" customHeight="1">
+    <row r="6" ht="42.6" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AscendOS is browser-delivered. Code Compass answers building-code questions against an ingested vector index; Code Inspector analyses site photographs; the estimating modules price work. Every one of them is a short job that holds a CPU core for seconds and then releases it, and most of that time is spent waiting on an external model API rather than computing.</t>
+          <t xml:space="preserve">AscendOS is browser-delivered. Code Compass answers building-code questions against an ingested vector index; Code Inspector analyses site photographs for code compliance. Both are short jobs that hold a CPU core for seconds and then release it, and most of that time is spent waiting on an external model API rather than computing.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42.6" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">SCOPE: Code Compass, and Code Compass plus Code Inspector. The estimating and tender modules exist in the product but are still in development and are not deployed to anyone, so they carry no load and appear nowhere in these figures. That is a deliberate exclusion, not an oversight - see the Assumptions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42.6" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">That behaviour is why the sizing is driven by HOW MANY JOBS RUN AT THE SAME MOMENT rather than by seat count or by requests per day. A few thousand searches spread across a working day resolve to a handful running simultaneously.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="6" customHeight="1"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The one column worth understanding: "running at the same time"</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42.6" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11" ht="42.6" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">It is not a fraction of a machine, and it is not how many people are logged in. It is how many searches are being worked on SIMULTANEOUSLY - how many people are sitting watching a spinner at the same instant, during the busiest hour of the day.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.2" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12" ht="16.2" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Take the 840-seat row. Read it left to right and it builds itself:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.2" customHeight="1">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   840 seats x (20 searches + 5 estimating jobs), plus 250 x 7 scans  =  22,750 jobs a day</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.2" customHeight="1">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the busy hour carries 3x its even share of those             =  8,531 in that hour</t>
+          <t xml:space="preserve">   840 seats x 20 searches, plus 250 people x 7 photo scans   =  18,550 jobs a day</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16.2" customHeight="1">
       <c r="A14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">   the busy hour carries 3x its even share of those             =  6,956 in that hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16.2" customHeight="1">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">   each one occupies a core for 12-55 seconds                   =  most finish before the next arrives</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.2" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   so at any given instant, mid-flight                          =  40 RUNNING AT ONCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42.6" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eight and a half thousand jobs an hour sounds enormous; 40 running simultaneously does not. Both are the same fact. A job takes seconds and then the core is free again, so they overlap far less than the daily total suggests. That overlap is the entire hardware question, and it is why 840 seats need about 12 vCPU rather than hundreds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="29.4" customHeight="1">
+    <row r="16" ht="16.2" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   so at any given instant, mid-flight                          =  31 RUNNING AT ONCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42.6" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A number below 1 is normal too. At 20 seats without Code Inspector it is 0.7 - meaning a job is in progress about that share of the busy hour and nothing is running the rest of it.</t>
+          <t xml:space="preserve">Nearly seven thousand jobs an hour sounds enormous; 31 running simultaneously does not. Both are the same fact. A job takes seconds and then the core is free again, so they overlap far less than the daily total suggests. That overlap is the entire hardware question, and it is why 840 seats need about 10 vCPU rather than hundreds.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29.4" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">It is an average, not a ceiling: arrivals are random, so short moments with two or three times the figure still happen, and the platform needs headroom to absorb them.</t>
+          <t xml:space="preserve">A number below 1 is normal too. At 20 seats with Code Compass alone it is 0.5 - meaning a search is in progress about half the busy hour and nothing is running the rest of it.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="29.4" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">It is an average, not a ceiling: arrivals are random, so short moments with two or three times the figure still happen, and the platform needs headroom to absorb them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29.4" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Job lengths differ by module: a Compass search runs about 12 seconds, an Inspector photo scan about 55. That is why a few hundred Inspector users move the figure more than several hundred extra Compass seats do.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The two cases</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42.6" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WITHOUT CODE INSPECTOR - every seat running Code Compass and the estimating modules. ALL MODULES - the same, plus 250 people also running Code Inspector, the most demanding configuration we would expect. Any real deployment sits between the two, so they bracket the answer rather than predicting it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="55.8" customHeight="1">
+    <row r="23" ht="42.6" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both are stated at the BUSY end of expected usage: 20 Code Compass searches and 5 estimating jobs per seat per working day, plus 7 Code Inspector scans per user. A platform sized on average usage is short on every busy day, so there is no point publishing the average. If usage settles at the quiet end (15, 3 and 5), every figure here is about a quarter lower.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="55.8" customHeight="1">
+          <t xml:space="preserve">CODE COMPASS ONLY - every seat running searches. CODE COMPASS + CODE INSPECTOR - the same, plus 250 people also running photo scans, the most demanding configuration currently in scope. Any real deployment sits between the two, so they bracket the answer rather than predicting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42.6" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDER SCANS ARE EXCLUDED. They are the heaviest job the platform runs - about 95 seconds and 13 model API calls each, against 12 seconds for a Compass search - and no rate has been established for them. They are left out rather than guessed at. If tenders are going to run regularly these figures need revisiting: even one per seat per week would add roughly 5 to the "running at the same time" column at 840 seats.</t>
+          <t xml:space="preserve">Both are stated at the BUSY end of expected usage: 20 Code Compass searches per seat per working day, plus 7 Code Inspector scans per user. A platform sized on average usage is short on every busy day, so there is no point publishing the average. If usage settles at the quiet end (15 and 5), every figure here is about a quarter lower.</t>
         </is>
       </c>
     </row>
@@ -412,7 +412,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WITHOUT CODE INSPECTOR  -  every seat running Code Compass and Estimating</t>
+          <t xml:space="preserve">CODE COMPASS ONLY  -  every seat running searches</t>
         </is>
       </c>
       <c r="B7" s="7"/>
@@ -429,7 +429,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jobs
+          <t xml:space="preserve">searches
 per day</t>
         </is>
       </c>
@@ -463,16 +463,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C9" s="14">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D9" s="13">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="4">
         <v>1.4</v>
@@ -483,19 +483,19 @@
         <v>100</v>
       </c>
       <c r="B10" s="14">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="C10" s="14">
-        <v>938</v>
+        <v>750</v>
       </c>
       <c r="D10" s="13">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E10" s="4">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="F10" s="4">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -503,19 +503,19 @@
         <v>200</v>
       </c>
       <c r="B11" s="14">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C11" s="14">
-        <v>1875</v>
+        <v>1500</v>
       </c>
       <c r="D11" s="13">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F11" s="4">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -523,19 +523,19 @@
         <v>300</v>
       </c>
       <c r="B12" s="14">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="C12" s="14">
-        <v>2813</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="13">
-        <v>10.6</v>
+        <v>7.5</v>
       </c>
       <c r="E12" s="4">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="F12" s="4">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="13">
@@ -543,19 +543,19 @@
         <v>400</v>
       </c>
       <c r="B13" s="14">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="C13" s="14">
-        <v>3750</v>
+        <v>3000</v>
       </c>
       <c r="D13" s="13">
-        <v>14.2</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="F13" s="4">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="14">
@@ -563,19 +563,19 @@
         <v>500</v>
       </c>
       <c r="B14" s="14">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="C14" s="14">
-        <v>4688</v>
+        <v>3750</v>
       </c>
       <c r="D14" s="13">
-        <v>17.7</v>
+        <v>12.5</v>
       </c>
       <c r="E14" s="4">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="F14" s="4">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="15">
@@ -583,19 +583,19 @@
         <v>600</v>
       </c>
       <c r="B15" s="14">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C15" s="14">
-        <v>5625</v>
+        <v>4500</v>
       </c>
       <c r="D15" s="13">
-        <v>21.3</v>
+        <v>15</v>
       </c>
       <c r="E15" s="4">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F15" s="4">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
@@ -603,19 +603,19 @@
         <v>700</v>
       </c>
       <c r="B16" s="14">
-        <v>17500</v>
+        <v>14000</v>
       </c>
       <c r="C16" s="14">
-        <v>6563</v>
+        <v>5250</v>
       </c>
       <c r="D16" s="13">
-        <v>24.8</v>
+        <v>17.5</v>
       </c>
       <c r="E16" s="4">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="F16" s="4">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
@@ -623,26 +623,26 @@
         <v>840</v>
       </c>
       <c r="B17" s="14">
-        <v>21000</v>
+        <v>16800</v>
       </c>
       <c r="C17" s="14">
-        <v>7875</v>
+        <v>6300</v>
       </c>
       <c r="D17" s="13">
-        <v>29.8</v>
+        <v>21</v>
       </c>
       <c r="E17" s="4">
-        <v>9.3</v>
+        <v>6.6</v>
       </c>
       <c r="F17" s="4">
-        <v>11.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL MODULES  -  the same, plus 250 people also running Code Inspector</t>
+          <t xml:space="preserve">CODE COMPASS + CODE INSPECTOR  -  the same, plus 250 people also running scans</t>
         </is>
       </c>
       <c r="B19" s="7"/>
@@ -693,16 +693,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="14">
-        <v>640</v>
+        <v>540</v>
       </c>
       <c r="C21" s="14">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="D21" s="13">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E21" s="4">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F21" s="4">
         <v>1.7</v>
@@ -713,19 +713,19 @@
         <v>100</v>
       </c>
       <c r="B22" s="14">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="C22" s="14">
-        <v>1200</v>
+        <v>1013</v>
       </c>
       <c r="D22" s="13">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="E22" s="4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="F22" s="4">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
@@ -733,19 +733,19 @@
         <v>200</v>
       </c>
       <c r="B23" s="14">
-        <v>6400</v>
+        <v>5400</v>
       </c>
       <c r="C23" s="14">
-        <v>2400</v>
+        <v>2025</v>
       </c>
       <c r="D23" s="13">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="E23" s="4">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F23" s="4">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="24">
@@ -753,19 +753,19 @@
         <v>300</v>
       </c>
       <c r="B24" s="14">
-        <v>9250</v>
+        <v>7750</v>
       </c>
       <c r="C24" s="14">
-        <v>3469</v>
+        <v>2906</v>
       </c>
       <c r="D24" s="13">
-        <v>20.7</v>
+        <v>17.5</v>
       </c>
       <c r="E24" s="4">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="F24" s="4">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="25">
@@ -773,19 +773,19 @@
         <v>400</v>
       </c>
       <c r="B25" s="14">
-        <v>11750</v>
+        <v>9750</v>
       </c>
       <c r="C25" s="14">
-        <v>4406</v>
+        <v>3656</v>
       </c>
       <c r="D25" s="13">
-        <v>24.2</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="F25" s="4">
-        <v>9.7</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="26">
@@ -793,19 +793,19 @@
         <v>500</v>
       </c>
       <c r="B26" s="14">
-        <v>14250</v>
+        <v>11750</v>
       </c>
       <c r="C26" s="14">
-        <v>5344</v>
+        <v>4406</v>
       </c>
       <c r="D26" s="13">
-        <v>27.7</v>
+        <v>22.5</v>
       </c>
       <c r="E26" s="4">
-        <v>8.7</v>
+        <v>7.1</v>
       </c>
       <c r="F26" s="4">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="27">
@@ -813,19 +813,19 @@
         <v>600</v>
       </c>
       <c r="B27" s="14">
-        <v>16750</v>
+        <v>13750</v>
       </c>
       <c r="C27" s="14">
-        <v>6281</v>
+        <v>5156</v>
       </c>
       <c r="D27" s="13">
-        <v>31.3</v>
+        <v>25</v>
       </c>
       <c r="E27" s="4">
-        <v>9.7</v>
+        <v>7.9</v>
       </c>
       <c r="F27" s="4">
-        <v>12.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -833,19 +833,19 @@
         <v>700</v>
       </c>
       <c r="B28" s="14">
-        <v>19250</v>
+        <v>15750</v>
       </c>
       <c r="C28" s="14">
-        <v>7219</v>
+        <v>5906</v>
       </c>
       <c r="D28" s="13">
-        <v>34.8</v>
+        <v>27.5</v>
       </c>
       <c r="E28" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="F28" s="4">
         <v>10.8</v>
-      </c>
-      <c r="F28" s="4">
-        <v>13.4</v>
       </c>
     </row>
     <row r="29">
@@ -853,19 +853,19 @@
         <v>840</v>
       </c>
       <c r="B29" s="14">
-        <v>22750</v>
+        <v>18550</v>
       </c>
       <c r="C29" s="14">
-        <v>8531</v>
+        <v>6956</v>
       </c>
       <c r="D29" s="13">
-        <v>39.8</v>
+        <v>31</v>
       </c>
       <c r="E29" s="4">
-        <v>12.3</v>
+        <v>9.7</v>
       </c>
       <c r="F29" s="4">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="30" ht="10" customHeight="1"/>
@@ -1149,7 +1149,7 @@
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WITHOUT CODE INSPECTOR  -  Compass and Estimating</t>
+          <t xml:space="preserve">CODE COMPASS ONLY</t>
         </is>
       </c>
       <c r="B4" s="7"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jobs
+          <t xml:space="preserve">searches
 per day</t>
         </is>
       </c>
@@ -1200,16 +1200,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C6" s="14">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D6" s="13">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="4">
         <v>1.4</v>
@@ -1220,19 +1220,19 @@
         <v>40</v>
       </c>
       <c r="B7" s="14">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C7" s="14">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="D7" s="13">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F7" s="4">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -1240,19 +1240,19 @@
         <v>60</v>
       </c>
       <c r="B8" s="14">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="C8" s="14">
-        <v>563</v>
+        <v>450</v>
       </c>
       <c r="D8" s="13">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="4">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -1260,19 +1260,19 @@
         <v>80</v>
       </c>
       <c r="B9" s="14">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="C9" s="14">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="D9" s="13">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="4">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -1280,19 +1280,19 @@
         <v>100</v>
       </c>
       <c r="B10" s="14">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="C10" s="14">
-        <v>938</v>
+        <v>750</v>
       </c>
       <c r="D10" s="13">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E10" s="4">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="F10" s="4">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -1300,19 +1300,19 @@
         <v>120</v>
       </c>
       <c r="B11" s="14">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="C11" s="14">
-        <v>1125</v>
+        <v>900</v>
       </c>
       <c r="D11" s="13">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F11" s="4">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -1320,19 +1320,19 @@
         <v>140</v>
       </c>
       <c r="B12" s="14">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="C12" s="14">
-        <v>1313</v>
+        <v>1050</v>
       </c>
       <c r="D12" s="13">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E12" s="4">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F12" s="4">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -1340,19 +1340,19 @@
         <v>160</v>
       </c>
       <c r="B13" s="14">
-        <v>4000</v>
+        <v>3200</v>
       </c>
       <c r="C13" s="14">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="13">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F13" s="4">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -1360,19 +1360,19 @@
         <v>180</v>
       </c>
       <c r="B14" s="14">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="C14" s="14">
-        <v>1688</v>
+        <v>1350</v>
       </c>
       <c r="D14" s="13">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="E14" s="4">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="F14" s="4">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1380,19 +1380,19 @@
         <v>200</v>
       </c>
       <c r="B15" s="14">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="C15" s="14">
-        <v>1875</v>
+        <v>1500</v>
       </c>
       <c r="D15" s="13">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F15" s="4">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1400,19 +1400,19 @@
         <v>220</v>
       </c>
       <c r="B16" s="14">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="C16" s="14">
-        <v>2063</v>
+        <v>1650</v>
       </c>
       <c r="D16" s="13">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="E16" s="4">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -1420,19 +1420,19 @@
         <v>240</v>
       </c>
       <c r="B17" s="14">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="C17" s="14">
-        <v>2250</v>
+        <v>1800</v>
       </c>
       <c r="D17" s="13">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="4">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="F17" s="4">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="18">
@@ -1440,19 +1440,19 @@
         <v>260</v>
       </c>
       <c r="B18" s="14">
-        <v>6500</v>
+        <v>5200</v>
       </c>
       <c r="C18" s="14">
-        <v>2438</v>
+        <v>1950</v>
       </c>
       <c r="D18" s="13">
-        <v>9.2</v>
+        <v>6.5</v>
       </c>
       <c r="E18" s="4">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="F18" s="4">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1460,19 +1460,19 @@
         <v>280</v>
       </c>
       <c r="B19" s="14">
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="C19" s="14">
-        <v>2625</v>
+        <v>2100</v>
       </c>
       <c r="D19" s="13">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="4">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="4">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -1480,19 +1480,19 @@
         <v>300</v>
       </c>
       <c r="B20" s="14">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="C20" s="14">
-        <v>2813</v>
+        <v>2250</v>
       </c>
       <c r="D20" s="13">
-        <v>10.6</v>
+        <v>7.5</v>
       </c>
       <c r="E20" s="4">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="F20" s="4">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="21">
@@ -1500,19 +1500,19 @@
         <v>320</v>
       </c>
       <c r="B21" s="14">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="C21" s="14">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="D21" s="13">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="E21" s="4">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="F21" s="4">
-        <v>5.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1520,19 +1520,19 @@
         <v>340</v>
       </c>
       <c r="B22" s="14">
-        <v>8500</v>
+        <v>6800</v>
       </c>
       <c r="C22" s="14">
-        <v>3188</v>
+        <v>2550</v>
       </c>
       <c r="D22" s="13">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="E22" s="4">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="F22" s="4">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="23">
@@ -1540,19 +1540,19 @@
         <v>360</v>
       </c>
       <c r="B23" s="14">
-        <v>9000</v>
+        <v>7200</v>
       </c>
       <c r="C23" s="14">
-        <v>3375</v>
+        <v>2700</v>
       </c>
       <c r="D23" s="13">
-        <v>12.8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="24">
@@ -1560,19 +1560,19 @@
         <v>380</v>
       </c>
       <c r="B24" s="14">
-        <v>9500</v>
+        <v>7600</v>
       </c>
       <c r="C24" s="14">
-        <v>3563</v>
+        <v>2850</v>
       </c>
       <c r="D24" s="13">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="E24" s="4">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="F24" s="4">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="25">
@@ -1580,19 +1580,19 @@
         <v>400</v>
       </c>
       <c r="B25" s="14">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="C25" s="14">
-        <v>3750</v>
+        <v>3000</v>
       </c>
       <c r="D25" s="13">
-        <v>14.2</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="F25" s="4">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -1600,19 +1600,19 @@
         <v>420</v>
       </c>
       <c r="B26" s="14">
-        <v>10500</v>
+        <v>8400</v>
       </c>
       <c r="C26" s="14">
-        <v>3938</v>
+        <v>3150</v>
       </c>
       <c r="D26" s="13">
-        <v>14.9</v>
+        <v>10.5</v>
       </c>
       <c r="E26" s="4">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="F26" s="4">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="27">
@@ -1620,19 +1620,19 @@
         <v>440</v>
       </c>
       <c r="B27" s="14">
-        <v>11000</v>
+        <v>8800</v>
       </c>
       <c r="C27" s="14">
-        <v>4125</v>
+        <v>3300</v>
       </c>
       <c r="D27" s="13">
-        <v>15.6</v>
+        <v>11</v>
       </c>
       <c r="E27" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="F27" s="4">
         <v>5</v>
-      </c>
-      <c r="F27" s="4">
-        <v>6.7</v>
       </c>
     </row>
     <row r="28">
@@ -1640,19 +1640,19 @@
         <v>460</v>
       </c>
       <c r="B28" s="14">
-        <v>11500</v>
+        <v>9200</v>
       </c>
       <c r="C28" s="14">
-        <v>4313</v>
+        <v>3450</v>
       </c>
       <c r="D28" s="13">
-        <v>16.3</v>
+        <v>11.5</v>
       </c>
       <c r="E28" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="F28" s="4">
         <v>5.2</v>
-      </c>
-      <c r="F28" s="4">
-        <v>6.9</v>
       </c>
     </row>
     <row r="29">
@@ -1660,19 +1660,19 @@
         <v>480</v>
       </c>
       <c r="B29" s="14">
-        <v>12000</v>
+        <v>9600</v>
       </c>
       <c r="C29" s="14">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="D29" s="13">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E29" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="F29" s="4">
         <v>5.4</v>
-      </c>
-      <c r="F29" s="4">
-        <v>7.1</v>
       </c>
     </row>
     <row r="30">
@@ -1680,19 +1680,19 @@
         <v>500</v>
       </c>
       <c r="B30" s="14">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="C30" s="14">
-        <v>4688</v>
+        <v>3750</v>
       </c>
       <c r="D30" s="13">
-        <v>17.7</v>
+        <v>12.5</v>
       </c>
       <c r="E30" s="4">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="F30" s="4">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31">
@@ -1700,19 +1700,19 @@
         <v>520</v>
       </c>
       <c r="B31" s="14">
-        <v>13000</v>
+        <v>10400</v>
       </c>
       <c r="C31" s="14">
-        <v>4875</v>
+        <v>3900</v>
       </c>
       <c r="D31" s="13">
-        <v>18.4</v>
+        <v>13</v>
       </c>
       <c r="E31" s="4">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="F31" s="4">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="32">
@@ -1720,19 +1720,19 @@
         <v>540</v>
       </c>
       <c r="B32" s="14">
-        <v>13500</v>
+        <v>10800</v>
       </c>
       <c r="C32" s="14">
-        <v>5063</v>
+        <v>4050</v>
       </c>
       <c r="D32" s="13">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="E32" s="4">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="F32" s="4">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="33">
@@ -1740,19 +1740,19 @@
         <v>560</v>
       </c>
       <c r="B33" s="14">
-        <v>14000</v>
+        <v>11200</v>
       </c>
       <c r="C33" s="14">
-        <v>5250</v>
+        <v>4200</v>
       </c>
       <c r="D33" s="13">
-        <v>19.8</v>
+        <v>14</v>
       </c>
       <c r="E33" s="4">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="F33" s="4">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="34">
@@ -1760,19 +1760,19 @@
         <v>580</v>
       </c>
       <c r="B34" s="14">
-        <v>14500</v>
+        <v>11600</v>
       </c>
       <c r="C34" s="14">
-        <v>5438</v>
+        <v>4350</v>
       </c>
       <c r="D34" s="13">
-        <v>20.5</v>
+        <v>14.5</v>
       </c>
       <c r="E34" s="4">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="F34" s="4">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="35">
@@ -1780,19 +1780,19 @@
         <v>600</v>
       </c>
       <c r="B35" s="14">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C35" s="14">
-        <v>5625</v>
+        <v>4500</v>
       </c>
       <c r="D35" s="13">
-        <v>21.3</v>
+        <v>15</v>
       </c>
       <c r="E35" s="4">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F35" s="4">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="36">
@@ -1800,19 +1800,19 @@
         <v>620</v>
       </c>
       <c r="B36" s="14">
-        <v>15500</v>
+        <v>12400</v>
       </c>
       <c r="C36" s="14">
-        <v>5813</v>
+        <v>4650</v>
       </c>
       <c r="D36" s="13">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="E36" s="4">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="F36" s="4">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="37">
@@ -1820,19 +1820,19 @@
         <v>640</v>
       </c>
       <c r="B37" s="14">
-        <v>16000</v>
+        <v>12800</v>
       </c>
       <c r="C37" s="14">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="D37" s="13">
-        <v>22.7</v>
+        <v>16</v>
       </c>
       <c r="E37" s="4">
-        <v>7.1</v>
+        <v>5.1</v>
       </c>
       <c r="F37" s="4">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="38">
@@ -1840,19 +1840,19 @@
         <v>660</v>
       </c>
       <c r="B38" s="14">
-        <v>16500</v>
+        <v>13200</v>
       </c>
       <c r="C38" s="14">
-        <v>6188</v>
+        <v>4950</v>
       </c>
       <c r="D38" s="13">
-        <v>23.4</v>
+        <v>16.5</v>
       </c>
       <c r="E38" s="4">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="F38" s="4">
-        <v>9.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1860,19 +1860,19 @@
         <v>680</v>
       </c>
       <c r="B39" s="14">
-        <v>17000</v>
+        <v>13600</v>
       </c>
       <c r="C39" s="14">
-        <v>6375</v>
+        <v>5100</v>
       </c>
       <c r="D39" s="13">
-        <v>24.1</v>
+        <v>17</v>
       </c>
       <c r="E39" s="4">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="F39" s="4">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="40">
@@ -1880,19 +1880,19 @@
         <v>700</v>
       </c>
       <c r="B40" s="14">
-        <v>17500</v>
+        <v>14000</v>
       </c>
       <c r="C40" s="14">
-        <v>6563</v>
+        <v>5250</v>
       </c>
       <c r="D40" s="13">
-        <v>24.8</v>
+        <v>17.5</v>
       </c>
       <c r="E40" s="4">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="F40" s="4">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="41">
@@ -1900,19 +1900,19 @@
         <v>720</v>
       </c>
       <c r="B41" s="14">
-        <v>18000</v>
+        <v>14400</v>
       </c>
       <c r="C41" s="14">
-        <v>6750</v>
+        <v>5400</v>
       </c>
       <c r="D41" s="13">
-        <v>25.5</v>
+        <v>18</v>
       </c>
       <c r="E41" s="4">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="F41" s="4">
-        <v>10.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="42">
@@ -1920,19 +1920,19 @@
         <v>740</v>
       </c>
       <c r="B42" s="14">
-        <v>18500</v>
+        <v>14800</v>
       </c>
       <c r="C42" s="14">
-        <v>6938</v>
+        <v>5550</v>
       </c>
       <c r="D42" s="13">
-        <v>26.2</v>
+        <v>18.5</v>
       </c>
       <c r="E42" s="4">
-        <v>8.2</v>
+        <v>5.9</v>
       </c>
       <c r="F42" s="4">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="43">
@@ -1940,19 +1940,19 @@
         <v>760</v>
       </c>
       <c r="B43" s="14">
-        <v>19000</v>
+        <v>15200</v>
       </c>
       <c r="C43" s="14">
-        <v>7125</v>
+        <v>5700</v>
       </c>
       <c r="D43" s="13">
-        <v>26.9</v>
+        <v>19</v>
       </c>
       <c r="E43" s="4">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="4">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="44">
@@ -1960,19 +1960,19 @@
         <v>780</v>
       </c>
       <c r="B44" s="14">
-        <v>19500</v>
+        <v>15600</v>
       </c>
       <c r="C44" s="14">
-        <v>7313</v>
+        <v>5850</v>
       </c>
       <c r="D44" s="13">
-        <v>27.6</v>
+        <v>19.5</v>
       </c>
       <c r="E44" s="4">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="F44" s="4">
-        <v>10.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1980,19 +1980,19 @@
         <v>800</v>
       </c>
       <c r="B45" s="14">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="C45" s="14">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="D45" s="13">
-        <v>28.3</v>
+        <v>20</v>
       </c>
       <c r="E45" s="4">
-        <v>8.8</v>
+        <v>6.3</v>
       </c>
       <c r="F45" s="4">
-        <v>11.1</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="46">
@@ -2000,19 +2000,19 @@
         <v>820</v>
       </c>
       <c r="B46" s="14">
-        <v>20500</v>
+        <v>16400</v>
       </c>
       <c r="C46" s="14">
-        <v>7688</v>
+        <v>6150</v>
       </c>
       <c r="D46" s="13">
-        <v>29</v>
+        <v>20.5</v>
       </c>
       <c r="E46" s="4">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="F46" s="4">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="47">
@@ -2020,26 +2020,26 @@
         <v>840</v>
       </c>
       <c r="B47" s="14">
-        <v>21000</v>
+        <v>16800</v>
       </c>
       <c r="C47" s="14">
-        <v>7875</v>
+        <v>6300</v>
       </c>
       <c r="D47" s="13">
-        <v>29.8</v>
+        <v>21</v>
       </c>
       <c r="E47" s="4">
-        <v>9.3</v>
+        <v>6.6</v>
       </c>
       <c r="F47" s="4">
-        <v>11.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="48" ht="10" customHeight="1"/>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALL MODULES  -  plus 250 Code Inspector users</t>
+          <t xml:space="preserve">CODE COMPASS + CODE INSPECTOR, 250 users</t>
         </is>
       </c>
       <c r="B49" s="7"/>
@@ -2090,16 +2090,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="14">
-        <v>640</v>
+        <v>540</v>
       </c>
       <c r="C51" s="14">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="D51" s="13">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E51" s="4">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F51" s="4">
         <v>1.7</v>
@@ -2110,19 +2110,19 @@
         <v>40</v>
       </c>
       <c r="B52" s="14">
-        <v>1280</v>
+        <v>1080</v>
       </c>
       <c r="C52" s="14">
-        <v>480</v>
+        <v>405</v>
       </c>
       <c r="D52" s="13">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="E52" s="4">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F52" s="4">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="53">
@@ -2130,19 +2130,19 @@
         <v>60</v>
       </c>
       <c r="B53" s="14">
-        <v>1920</v>
+        <v>1620</v>
       </c>
       <c r="C53" s="14">
-        <v>720</v>
+        <v>608</v>
       </c>
       <c r="D53" s="13">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="E53" s="4">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="F53" s="4">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="54">
@@ -2150,19 +2150,19 @@
         <v>80</v>
       </c>
       <c r="B54" s="14">
-        <v>2560</v>
+        <v>2160</v>
       </c>
       <c r="C54" s="14">
-        <v>960</v>
+        <v>810</v>
       </c>
       <c r="D54" s="13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E54" s="4">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="F54" s="4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2170,19 +2170,19 @@
         <v>100</v>
       </c>
       <c r="B55" s="14">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="C55" s="14">
-        <v>1200</v>
+        <v>1013</v>
       </c>
       <c r="D55" s="13">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="E55" s="4">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="F55" s="4">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="56">
@@ -2190,19 +2190,19 @@
         <v>120</v>
       </c>
       <c r="B56" s="14">
-        <v>3840</v>
+        <v>3240</v>
       </c>
       <c r="C56" s="14">
-        <v>1440</v>
+        <v>1215</v>
       </c>
       <c r="D56" s="13">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="E56" s="4">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="F56" s="4">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="57">
@@ -2210,19 +2210,19 @@
         <v>140</v>
       </c>
       <c r="B57" s="14">
-        <v>4480</v>
+        <v>3780</v>
       </c>
       <c r="C57" s="14">
-        <v>1680</v>
+        <v>1418</v>
       </c>
       <c r="D57" s="13">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="E57" s="4">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F57" s="4">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="58">
@@ -2230,19 +2230,19 @@
         <v>160</v>
       </c>
       <c r="B58" s="14">
-        <v>5120</v>
+        <v>4320</v>
       </c>
       <c r="C58" s="14">
-        <v>1920</v>
+        <v>1620</v>
       </c>
       <c r="D58" s="13">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" s="4">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F58" s="4">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="59">
@@ -2250,19 +2250,19 @@
         <v>180</v>
       </c>
       <c r="B59" s="14">
-        <v>5760</v>
+        <v>4860</v>
       </c>
       <c r="C59" s="14">
-        <v>2160</v>
+        <v>1823</v>
       </c>
       <c r="D59" s="13">
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
       <c r="E59" s="4">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="F59" s="4">
-        <v>6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="60">
@@ -2270,19 +2270,19 @@
         <v>200</v>
       </c>
       <c r="B60" s="14">
-        <v>6400</v>
+        <v>5400</v>
       </c>
       <c r="C60" s="14">
-        <v>2400</v>
+        <v>2025</v>
       </c>
       <c r="D60" s="13">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="E60" s="4">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F60" s="4">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="61">
@@ -2290,19 +2290,19 @@
         <v>220</v>
       </c>
       <c r="B61" s="14">
-        <v>7040</v>
+        <v>5940</v>
       </c>
       <c r="C61" s="14">
-        <v>2640</v>
+        <v>2228</v>
       </c>
       <c r="D61" s="13">
-        <v>16.6</v>
+        <v>14.3</v>
       </c>
       <c r="E61" s="4">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="F61" s="4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
@@ -2310,19 +2310,19 @@
         <v>240</v>
       </c>
       <c r="B62" s="14">
-        <v>7680</v>
+        <v>6480</v>
       </c>
       <c r="C62" s="14">
-        <v>2880</v>
+        <v>2430</v>
       </c>
       <c r="D62" s="13">
-        <v>18.1</v>
+        <v>15.6</v>
       </c>
       <c r="E62" s="4">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="F62" s="4">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="63">
@@ -2330,19 +2330,19 @@
         <v>260</v>
       </c>
       <c r="B63" s="14">
-        <v>8250</v>
+        <v>6950</v>
       </c>
       <c r="C63" s="14">
-        <v>3094</v>
+        <v>2606</v>
       </c>
       <c r="D63" s="13">
-        <v>19.2</v>
+        <v>16.5</v>
       </c>
       <c r="E63" s="4">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="F63" s="4">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2350,19 +2350,19 @@
         <v>280</v>
       </c>
       <c r="B64" s="14">
-        <v>8750</v>
+        <v>7350</v>
       </c>
       <c r="C64" s="14">
-        <v>3281</v>
+        <v>2756</v>
       </c>
       <c r="D64" s="13">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="E64" s="4">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="F64" s="4">
-        <v>8.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="65">
@@ -2370,19 +2370,19 @@
         <v>300</v>
       </c>
       <c r="B65" s="14">
-        <v>9250</v>
+        <v>7750</v>
       </c>
       <c r="C65" s="14">
-        <v>3469</v>
+        <v>2906</v>
       </c>
       <c r="D65" s="13">
-        <v>20.7</v>
+        <v>17.5</v>
       </c>
       <c r="E65" s="4">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="F65" s="4">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="66">
@@ -2390,19 +2390,19 @@
         <v>320</v>
       </c>
       <c r="B66" s="14">
-        <v>9750</v>
+        <v>8150</v>
       </c>
       <c r="C66" s="14">
-        <v>3656</v>
+        <v>3056</v>
       </c>
       <c r="D66" s="13">
-        <v>21.4</v>
+        <v>18</v>
       </c>
       <c r="E66" s="4">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="F66" s="4">
-        <v>8.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="67">
@@ -2410,19 +2410,19 @@
         <v>340</v>
       </c>
       <c r="B67" s="14">
-        <v>10250</v>
+        <v>8550</v>
       </c>
       <c r="C67" s="14">
-        <v>3844</v>
+        <v>3206</v>
       </c>
       <c r="D67" s="13">
-        <v>22.1</v>
+        <v>18.5</v>
       </c>
       <c r="E67" s="4">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="F67" s="4">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
@@ -2430,19 +2430,19 @@
         <v>360</v>
       </c>
       <c r="B68" s="14">
-        <v>10750</v>
+        <v>8950</v>
       </c>
       <c r="C68" s="14">
-        <v>4031</v>
+        <v>3356</v>
       </c>
       <c r="D68" s="13">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="E68" s="4">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="F68" s="4">
-        <v>9.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="69">
@@ -2450,19 +2450,19 @@
         <v>380</v>
       </c>
       <c r="B69" s="14">
-        <v>11250</v>
+        <v>9350</v>
       </c>
       <c r="C69" s="14">
-        <v>4219</v>
+        <v>3506</v>
       </c>
       <c r="D69" s="13">
-        <v>23.5</v>
+        <v>19.5</v>
       </c>
       <c r="E69" s="4">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="F69" s="4">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -2470,19 +2470,19 @@
         <v>400</v>
       </c>
       <c r="B70" s="14">
-        <v>11750</v>
+        <v>9750</v>
       </c>
       <c r="C70" s="14">
-        <v>4406</v>
+        <v>3656</v>
       </c>
       <c r="D70" s="13">
-        <v>24.2</v>
+        <v>20</v>
       </c>
       <c r="E70" s="4">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="F70" s="4">
-        <v>9.7</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="71">
@@ -2490,19 +2490,19 @@
         <v>420</v>
       </c>
       <c r="B71" s="14">
-        <v>12250</v>
+        <v>10150</v>
       </c>
       <c r="C71" s="14">
-        <v>4594</v>
+        <v>3806</v>
       </c>
       <c r="D71" s="13">
-        <v>24.9</v>
+        <v>20.5</v>
       </c>
       <c r="E71" s="4">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="F71" s="4">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="72">
@@ -2510,19 +2510,19 @@
         <v>440</v>
       </c>
       <c r="B72" s="14">
-        <v>12750</v>
+        <v>10550</v>
       </c>
       <c r="C72" s="14">
-        <v>4781</v>
+        <v>3956</v>
       </c>
       <c r="D72" s="13">
-        <v>25.6</v>
+        <v>21</v>
       </c>
       <c r="E72" s="4">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="F72" s="4">
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="73">
@@ -2530,19 +2530,19 @@
         <v>460</v>
       </c>
       <c r="B73" s="14">
-        <v>13250</v>
+        <v>10950</v>
       </c>
       <c r="C73" s="14">
-        <v>4969</v>
+        <v>4106</v>
       </c>
       <c r="D73" s="13">
-        <v>26.3</v>
+        <v>21.5</v>
       </c>
       <c r="E73" s="4">
-        <v>8.2</v>
+        <v>6.8</v>
       </c>
       <c r="F73" s="4">
-        <v>10.4</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="74">
@@ -2550,19 +2550,19 @@
         <v>480</v>
       </c>
       <c r="B74" s="14">
-        <v>13750</v>
+        <v>11350</v>
       </c>
       <c r="C74" s="14">
-        <v>5156</v>
+        <v>4256</v>
       </c>
       <c r="D74" s="13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E74" s="4">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="F74" s="4">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="75">
@@ -2570,19 +2570,19 @@
         <v>500</v>
       </c>
       <c r="B75" s="14">
-        <v>14250</v>
+        <v>11750</v>
       </c>
       <c r="C75" s="14">
-        <v>5344</v>
+        <v>4406</v>
       </c>
       <c r="D75" s="13">
-        <v>27.7</v>
+        <v>22.5</v>
       </c>
       <c r="E75" s="4">
-        <v>8.7</v>
+        <v>7.1</v>
       </c>
       <c r="F75" s="4">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="76">
@@ -2590,19 +2590,19 @@
         <v>520</v>
       </c>
       <c r="B76" s="14">
-        <v>14750</v>
+        <v>12150</v>
       </c>
       <c r="C76" s="14">
-        <v>5531</v>
+        <v>4556</v>
       </c>
       <c r="D76" s="13">
-        <v>28.4</v>
+        <v>23</v>
       </c>
       <c r="E76" s="4">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="F76" s="4">
-        <v>11.2</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="77">
@@ -2610,19 +2610,19 @@
         <v>540</v>
       </c>
       <c r="B77" s="14">
-        <v>15250</v>
+        <v>12550</v>
       </c>
       <c r="C77" s="14">
-        <v>5719</v>
+        <v>4706</v>
       </c>
       <c r="D77" s="13">
-        <v>29.2</v>
+        <v>23.5</v>
       </c>
       <c r="E77" s="4">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="F77" s="4">
-        <v>11.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="78">
@@ -2630,19 +2630,19 @@
         <v>560</v>
       </c>
       <c r="B78" s="14">
-        <v>15750</v>
+        <v>12950</v>
       </c>
       <c r="C78" s="14">
-        <v>5906</v>
+        <v>4856</v>
       </c>
       <c r="D78" s="13">
-        <v>29.9</v>
+        <v>24</v>
       </c>
       <c r="E78" s="4">
-        <v>9.3</v>
+        <v>7.6</v>
       </c>
       <c r="F78" s="4">
-        <v>11.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="79">
@@ -2650,19 +2650,19 @@
         <v>580</v>
       </c>
       <c r="B79" s="14">
-        <v>16250</v>
+        <v>13350</v>
       </c>
       <c r="C79" s="14">
-        <v>6094</v>
+        <v>5006</v>
       </c>
       <c r="D79" s="13">
-        <v>30.6</v>
+        <v>24.5</v>
       </c>
       <c r="E79" s="4">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="F79" s="4">
-        <v>11.9</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="80">
@@ -2670,19 +2670,19 @@
         <v>600</v>
       </c>
       <c r="B80" s="14">
-        <v>16750</v>
+        <v>13750</v>
       </c>
       <c r="C80" s="14">
-        <v>6281</v>
+        <v>5156</v>
       </c>
       <c r="D80" s="13">
-        <v>31.3</v>
+        <v>25</v>
       </c>
       <c r="E80" s="4">
-        <v>9.7</v>
+        <v>7.9</v>
       </c>
       <c r="F80" s="4">
-        <v>12.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -2690,19 +2690,19 @@
         <v>620</v>
       </c>
       <c r="B81" s="14">
-        <v>17250</v>
+        <v>14150</v>
       </c>
       <c r="C81" s="14">
-        <v>6469</v>
+        <v>5306</v>
       </c>
       <c r="D81" s="13">
-        <v>32</v>
+        <v>25.5</v>
       </c>
       <c r="E81" s="4">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="F81" s="4">
-        <v>12.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="82">
@@ -2710,19 +2710,19 @@
         <v>640</v>
       </c>
       <c r="B82" s="14">
-        <v>17750</v>
+        <v>14550</v>
       </c>
       <c r="C82" s="14">
-        <v>6656</v>
+        <v>5456</v>
       </c>
       <c r="D82" s="13">
-        <v>32.7</v>
+        <v>26</v>
       </c>
       <c r="E82" s="4">
-        <v>10.2</v>
+        <v>8.2</v>
       </c>
       <c r="F82" s="4">
-        <v>12.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="83">
@@ -2730,19 +2730,19 @@
         <v>660</v>
       </c>
       <c r="B83" s="14">
-        <v>18250</v>
+        <v>14950</v>
       </c>
       <c r="C83" s="14">
-        <v>6844</v>
+        <v>5606</v>
       </c>
       <c r="D83" s="13">
-        <v>33.4</v>
+        <v>26.5</v>
       </c>
       <c r="E83" s="4">
-        <v>10.4</v>
+        <v>8.3</v>
       </c>
       <c r="F83" s="4">
-        <v>12.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="84">
@@ -2750,19 +2750,19 @@
         <v>680</v>
       </c>
       <c r="B84" s="14">
-        <v>18750</v>
+        <v>15350</v>
       </c>
       <c r="C84" s="14">
-        <v>7031</v>
+        <v>5756</v>
       </c>
       <c r="D84" s="13">
-        <v>34.1</v>
+        <v>27</v>
       </c>
       <c r="E84" s="4">
-        <v>10.6</v>
+        <v>8.5</v>
       </c>
       <c r="F84" s="4">
-        <v>13.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="85">
@@ -2770,19 +2770,19 @@
         <v>700</v>
       </c>
       <c r="B85" s="14">
-        <v>19250</v>
+        <v>15750</v>
       </c>
       <c r="C85" s="14">
-        <v>7219</v>
+        <v>5906</v>
       </c>
       <c r="D85" s="13">
-        <v>34.8</v>
+        <v>27.5</v>
       </c>
       <c r="E85" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="F85" s="4">
         <v>10.8</v>
-      </c>
-      <c r="F85" s="4">
-        <v>13.4</v>
       </c>
     </row>
     <row r="86">
@@ -2790,19 +2790,19 @@
         <v>720</v>
       </c>
       <c r="B86" s="14">
-        <v>19750</v>
+        <v>16150</v>
       </c>
       <c r="C86" s="14">
-        <v>7406</v>
+        <v>6056</v>
       </c>
       <c r="D86" s="13">
-        <v>35.5</v>
+        <v>28</v>
       </c>
       <c r="E86" s="4">
+        <v>8.8</v>
+      </c>
+      <c r="F86" s="4">
         <v>11</v>
-      </c>
-      <c r="F86" s="4">
-        <v>13.6</v>
       </c>
     </row>
     <row r="87">
@@ -2810,19 +2810,19 @@
         <v>740</v>
       </c>
       <c r="B87" s="14">
-        <v>20250</v>
+        <v>16550</v>
       </c>
       <c r="C87" s="14">
-        <v>7594</v>
+        <v>6206</v>
       </c>
       <c r="D87" s="13">
-        <v>36.2</v>
+        <v>28.5</v>
       </c>
       <c r="E87" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="F87" s="4">
         <v>11.2</v>
-      </c>
-      <c r="F87" s="4">
-        <v>13.9</v>
       </c>
     </row>
     <row r="88">
@@ -2830,19 +2830,19 @@
         <v>760</v>
       </c>
       <c r="B88" s="14">
-        <v>20750</v>
+        <v>16950</v>
       </c>
       <c r="C88" s="14">
-        <v>7781</v>
+        <v>6356</v>
       </c>
       <c r="D88" s="13">
-        <v>36.9</v>
+        <v>29</v>
       </c>
       <c r="E88" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="F88" s="4">
         <v>11.4</v>
-      </c>
-      <c r="F88" s="4">
-        <v>14.1</v>
       </c>
     </row>
     <row r="89">
@@ -2850,19 +2850,19 @@
         <v>780</v>
       </c>
       <c r="B89" s="14">
-        <v>21250</v>
+        <v>17350</v>
       </c>
       <c r="C89" s="14">
-        <v>7969</v>
+        <v>6506</v>
       </c>
       <c r="D89" s="13">
-        <v>37.7</v>
+        <v>29.5</v>
       </c>
       <c r="E89" s="4">
-        <v>11.6</v>
+        <v>9.2</v>
       </c>
       <c r="F89" s="4">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="90">
@@ -2870,19 +2870,19 @@
         <v>800</v>
       </c>
       <c r="B90" s="14">
-        <v>21750</v>
+        <v>17750</v>
       </c>
       <c r="C90" s="14">
-        <v>8156</v>
+        <v>6656</v>
       </c>
       <c r="D90" s="13">
-        <v>38.4</v>
+        <v>30</v>
       </c>
       <c r="E90" s="4">
-        <v>11.9</v>
+        <v>9.4</v>
       </c>
       <c r="F90" s="4">
-        <v>14.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="91">
@@ -2890,19 +2890,19 @@
         <v>820</v>
       </c>
       <c r="B91" s="14">
-        <v>22250</v>
+        <v>18150</v>
       </c>
       <c r="C91" s="14">
-        <v>8344</v>
+        <v>6806</v>
       </c>
       <c r="D91" s="13">
-        <v>39.1</v>
+        <v>30.5</v>
       </c>
       <c r="E91" s="4">
-        <v>12.1</v>
+        <v>9.5</v>
       </c>
       <c r="F91" s="4">
-        <v>14.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="92">
@@ -2910,19 +2910,19 @@
         <v>840</v>
       </c>
       <c r="B92" s="14">
-        <v>22750</v>
+        <v>18550</v>
       </c>
       <c r="C92" s="14">
-        <v>8531</v>
+        <v>6956</v>
       </c>
       <c r="D92" s="13">
-        <v>39.8</v>
+        <v>31</v>
       </c>
       <c r="E92" s="4">
-        <v>12.3</v>
+        <v>9.7</v>
       </c>
       <c r="F92" s="4">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="93" ht="10" customHeight="1"/>
@@ -3002,12 +3002,12 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimating jobs</t>
+          <t xml:space="preserve">Estimating module</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3–5 per seat per working day</t>
+          <t xml:space="preserve">NOT IN SCOPE — still in development, not deployed</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -3036,17 +3036,17 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender scans</t>
+          <t xml:space="preserve">Tender module</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXCLUDED — no rate established</t>
+          <t xml:space="preserve">NOT IN SCOPE — still in development, not deployed</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaviest job on the platform. See note below</t>
+          <t xml:space="preserve">Stated by Ironwood</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 seconds, 3 model API calls</t>
+          <t xml:space="preserve">20 seconds, 3 model API calls — if it ships</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 seconds, 13 model API calls</t>
+          <t xml:space="preserve">95 seconds, 13 model API calls — if it ships</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -3309,37 +3309,96 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The one open item</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42.6" customHeight="1">
+          <t xml:space="preserve">Modules not in scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="29.4" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender scans are excluded because no usage rate has been established for them, and they are by some distance the heaviest job the platform runs - roughly 95 seconds and 13 model API calls each. Everything else above is either measured or stated. If tender scanning is going to be part of normal use, these figures need redoing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
+          <t xml:space="preserve">The estimating and tender modules are in development and deployed to nobody, so they carry no load. Their job durations appear above only so the effect of releasing them can be judged without rebuilding this document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If it ships</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At this rate</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adds at 840 seats</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimating</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 per seat per day</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+8.8 running at once, +2.6 vCPU, +3.1 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tender scans</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 per seat per week</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+1.7 running at once, +0.5 vCPU, +0.6 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16.2" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neither would change the storage or network requirements - only the application tier grows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Derived, not assumed</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42.6" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="33" ht="42.6" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">The vCPU and memory figures come from the two coefficients at the bottom of the table applied to the concurrency figure, which itself comes from the usage rates and job durations above it. Nothing in the requirement columns is a judgement laid on top - change an input and the whole chain moves with it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
